--- a/research/traditional_assets/database/data/new_zealand/new_zealand_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_oil_gas_distribution.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07031265058164096</v>
+        <v>0.07014817516001236</v>
       </c>
       <c r="C2">
-        <v>505.7049404744717</v>
+        <v>502.4607047857404</v>
       </c>
       <c r="D2">
-        <v>504.8819404744717</v>
+        <v>507.7507047857404</v>
       </c>
       <c r="E2">
-        <v>-200.3</v>
+        <v>-194.187</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.113</v>
       </c>
       <c r="G2">
         <v>0.823</v>
@@ -1457,28 +1457,28 @@
         <v>46.775</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3074839</v>
       </c>
       <c r="N2">
-        <v>46.775</v>
+        <v>46.4675161</v>
       </c>
       <c r="O2">
-        <v>13.097</v>
+        <v>13.010904508</v>
       </c>
       <c r="P2">
-        <v>33.678</v>
+        <v>33.45661159199999</v>
       </c>
       <c r="Q2">
-        <v>56.778</v>
+        <v>56.556611592</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07031265058164096</v>
+        <v>0.07049092440405288</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5702292010173878</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>152.121785888627</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07014817516001236</v>
+        <v>0.06998369973838375</v>
       </c>
       <c r="C3">
-        <v>502.4607047857404</v>
+        <v>499.2492563187969</v>
       </c>
       <c r="D3">
-        <v>507.7507047857404</v>
+        <v>510.652256318797</v>
       </c>
       <c r="E3">
-        <v>-194.187</v>
+        <v>-188.074</v>
       </c>
       <c r="F3">
-        <v>6.113</v>
+        <v>12.226</v>
       </c>
       <c r="G3">
         <v>0.823</v>
@@ -1539,28 +1539,28 @@
         <v>46.775</v>
       </c>
       <c r="M3">
-        <v>0.3074839</v>
+        <v>0.6149678</v>
       </c>
       <c r="N3">
-        <v>46.4675161</v>
+        <v>46.1600322</v>
       </c>
       <c r="O3">
-        <v>13.010904508</v>
+        <v>12.924809016</v>
       </c>
       <c r="P3">
-        <v>33.45661159199999</v>
+        <v>33.235223184</v>
       </c>
       <c r="Q3">
-        <v>56.556611592</v>
+        <v>56.335223184</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07049092440405288</v>
+        <v>0.07067283646773853</v>
       </c>
       <c r="T3">
-        <v>0.5702292010173878</v>
+        <v>0.5744304034119755</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>152.121785888627</v>
+        <v>76.06089294431351</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06998369973838375</v>
+        <v>0.06981922431675518</v>
       </c>
       <c r="C4">
-        <v>499.2492563187969</v>
+        <v>496.0711603938736</v>
       </c>
       <c r="D4">
-        <v>510.652256318797</v>
+        <v>513.5871603938737</v>
       </c>
       <c r="E4">
-        <v>-188.074</v>
+        <v>-181.961</v>
       </c>
       <c r="F4">
-        <v>12.226</v>
+        <v>18.339</v>
       </c>
       <c r="G4">
         <v>0.823</v>
@@ -1621,28 +1621,28 @@
         <v>46.775</v>
       </c>
       <c r="M4">
-        <v>0.6149678</v>
+        <v>0.9224516999999999</v>
       </c>
       <c r="N4">
-        <v>46.1600322</v>
+        <v>45.8525483</v>
       </c>
       <c r="O4">
-        <v>12.924809016</v>
+        <v>12.838713524</v>
       </c>
       <c r="P4">
-        <v>33.235223184</v>
+        <v>33.013834776</v>
       </c>
       <c r="Q4">
-        <v>56.335223184</v>
+        <v>56.113834776</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07067283646773853</v>
+        <v>0.07085849929562389</v>
       </c>
       <c r="T4">
-        <v>0.5744304034119755</v>
+        <v>0.5787182285363485</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>76.06089294431351</v>
+        <v>50.70726196287567</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06981922431675518</v>
+        <v>0.06965474889512657</v>
       </c>
       <c r="C5">
-        <v>496.0711603938736</v>
+        <v>492.9269954027344</v>
       </c>
       <c r="D5">
-        <v>513.5871603938737</v>
+        <v>516.5559954027344</v>
       </c>
       <c r="E5">
-        <v>-181.961</v>
+        <v>-175.848</v>
       </c>
       <c r="F5">
-        <v>18.339</v>
+        <v>24.452</v>
       </c>
       <c r="G5">
         <v>0.823</v>
@@ -1703,28 +1703,28 @@
         <v>46.775</v>
       </c>
       <c r="M5">
-        <v>0.9224516999999999</v>
+        <v>1.2299356</v>
       </c>
       <c r="N5">
-        <v>45.8525483</v>
+        <v>45.5450644</v>
       </c>
       <c r="O5">
-        <v>12.838713524</v>
+        <v>12.752618032</v>
       </c>
       <c r="P5">
-        <v>33.013834776</v>
+        <v>32.792446368</v>
       </c>
       <c r="Q5">
-        <v>56.113834776</v>
+        <v>55.892446368</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07085849929562389</v>
+        <v>0.07104803009909018</v>
       </c>
       <c r="T5">
-        <v>0.5787182285363485</v>
+        <v>0.5830953833508126</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.70726196287567</v>
+        <v>38.03044647215675</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06965474889512657</v>
+        <v>0.06949027347349798</v>
       </c>
       <c r="C6">
-        <v>492.9269954027344</v>
+        <v>489.8173531886738</v>
       </c>
       <c r="D6">
-        <v>516.5559954027344</v>
+        <v>519.5593531886739</v>
       </c>
       <c r="E6">
-        <v>-175.848</v>
+        <v>-169.735</v>
       </c>
       <c r="F6">
-        <v>24.452</v>
+        <v>30.565</v>
       </c>
       <c r="G6">
         <v>0.823</v>
@@ -1785,28 +1785,28 @@
         <v>46.775</v>
       </c>
       <c r="M6">
-        <v>1.2299356</v>
+        <v>1.5374195</v>
       </c>
       <c r="N6">
-        <v>45.5450644</v>
+        <v>45.2375805</v>
       </c>
       <c r="O6">
-        <v>12.752618032</v>
+        <v>12.66652254</v>
       </c>
       <c r="P6">
-        <v>32.792446368</v>
+        <v>32.57105796</v>
       </c>
       <c r="Q6">
-        <v>55.892446368</v>
+        <v>55.67105796</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07104803009909018</v>
+        <v>0.07124155102473471</v>
       </c>
       <c r="T6">
-        <v>0.5830953833508126</v>
+        <v>0.5875646887929495</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.03044647215675</v>
+        <v>30.42435717772541</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06949027347349798</v>
+        <v>0.06932579805186938</v>
       </c>
       <c r="C7">
-        <v>489.8173531886738</v>
+        <v>486.7428394398562</v>
       </c>
       <c r="D7">
-        <v>519.5593531886739</v>
+        <v>522.5978394398562</v>
       </c>
       <c r="E7">
-        <v>-169.735</v>
+        <v>-163.622</v>
       </c>
       <c r="F7">
-        <v>30.565</v>
+        <v>36.678</v>
       </c>
       <c r="G7">
         <v>0.823</v>
@@ -1867,28 +1867,28 @@
         <v>46.775</v>
       </c>
       <c r="M7">
-        <v>1.5374195</v>
+        <v>1.8449034</v>
       </c>
       <c r="N7">
-        <v>45.2375805</v>
+        <v>44.9300966</v>
       </c>
       <c r="O7">
-        <v>12.66652254</v>
+        <v>12.580427048</v>
       </c>
       <c r="P7">
-        <v>32.57105796</v>
+        <v>32.34966955199999</v>
       </c>
       <c r="Q7">
-        <v>55.67105796</v>
+        <v>55.449669552</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07124155102473471</v>
+        <v>0.07143918941688232</v>
       </c>
       <c r="T7">
-        <v>0.5875646887929495</v>
+        <v>0.5921290858402385</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.42435717772541</v>
+        <v>25.35363098143784</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06932579805186938</v>
+        <v>0.0691613226302408</v>
       </c>
       <c r="C8">
-        <v>486.7428394398562</v>
+        <v>483.7040740965317</v>
       </c>
       <c r="D8">
-        <v>522.5978394398562</v>
+        <v>525.6720740965317</v>
       </c>
       <c r="E8">
-        <v>-163.622</v>
+        <v>-157.509</v>
       </c>
       <c r="F8">
-        <v>36.678</v>
+        <v>42.79099999999999</v>
       </c>
       <c r="G8">
         <v>0.823</v>
@@ -1949,28 +1949,28 @@
         <v>46.775</v>
       </c>
       <c r="M8">
-        <v>1.8449034</v>
+        <v>2.1523873</v>
       </c>
       <c r="N8">
-        <v>44.9300966</v>
+        <v>44.6226127</v>
       </c>
       <c r="O8">
-        <v>12.580427048</v>
+        <v>12.494331556</v>
       </c>
       <c r="P8">
-        <v>32.34966955199999</v>
+        <v>32.128281144</v>
       </c>
       <c r="Q8">
-        <v>55.449669552</v>
+        <v>55.228281144</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07143918941688232</v>
+        <v>0.07164107809703311</v>
       </c>
       <c r="T8">
-        <v>0.5921290858402385</v>
+        <v>0.5967916419638132</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.35363098143784</v>
+        <v>21.73168369837529</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06916132263024079</v>
+        <v>0.0689968472086122</v>
       </c>
       <c r="C9">
-        <v>483.704074096532</v>
+        <v>480.7016917727175</v>
       </c>
       <c r="D9">
-        <v>525.672074096532</v>
+        <v>528.7826917727175</v>
       </c>
       <c r="E9">
-        <v>-157.509</v>
+        <v>-151.396</v>
       </c>
       <c r="F9">
-        <v>42.791</v>
+        <v>48.904</v>
       </c>
       <c r="G9">
         <v>0.823</v>
@@ -2031,28 +2031,28 @@
         <v>46.775</v>
       </c>
       <c r="M9">
-        <v>2.1523873</v>
+        <v>2.4598712</v>
       </c>
       <c r="N9">
-        <v>44.6226127</v>
+        <v>44.3151288</v>
       </c>
       <c r="O9">
-        <v>12.494331556</v>
+        <v>12.408236064</v>
       </c>
       <c r="P9">
-        <v>32.128281144</v>
+        <v>31.906892736</v>
       </c>
       <c r="Q9">
-        <v>55.228281144</v>
+        <v>55.006892736</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07164107809703311</v>
+        <v>0.071847355661535</v>
       </c>
       <c r="T9">
-        <v>0.5967916419638132</v>
+        <v>0.6015555580031178</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.73168369837529</v>
+        <v>19.01522323607838</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0689968472086122</v>
+        <v>0.06883237178698361</v>
       </c>
       <c r="C10">
-        <v>480.7016917727175</v>
+        <v>477.7363421929315</v>
       </c>
       <c r="D10">
-        <v>528.7826917727175</v>
+        <v>531.9303421929316</v>
       </c>
       <c r="E10">
-        <v>-151.396</v>
+        <v>-145.283</v>
       </c>
       <c r="F10">
-        <v>48.904</v>
+        <v>55.017</v>
       </c>
       <c r="G10">
         <v>0.823</v>
@@ -2113,28 +2113,28 @@
         <v>46.775</v>
       </c>
       <c r="M10">
-        <v>2.4598712</v>
+        <v>2.7673551</v>
       </c>
       <c r="N10">
-        <v>44.3151288</v>
+        <v>44.0076449</v>
       </c>
       <c r="O10">
-        <v>12.408236064</v>
+        <v>12.322140572</v>
       </c>
       <c r="P10">
-        <v>31.906892736</v>
+        <v>31.685504328</v>
       </c>
       <c r="Q10">
-        <v>55.006892736</v>
+        <v>54.785504328</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.071847355661535</v>
+        <v>0.07205816679888308</v>
       </c>
       <c r="T10">
-        <v>0.6015555580031178</v>
+        <v>0.6064241754938356</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.01522323607838</v>
+        <v>16.90242065429189</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06883237178698361</v>
+        <v>0.068667896365355</v>
       </c>
       <c r="C11">
-        <v>477.7363421929315</v>
+        <v>474.8086906446255</v>
       </c>
       <c r="D11">
-        <v>531.9303421929316</v>
+        <v>535.1156906446255</v>
       </c>
       <c r="E11">
-        <v>-145.283</v>
+        <v>-139.17</v>
       </c>
       <c r="F11">
-        <v>55.017</v>
+        <v>61.12999999999999</v>
       </c>
       <c r="G11">
         <v>0.823</v>
@@ -2195,28 +2195,28 @@
         <v>46.775</v>
       </c>
       <c r="M11">
-        <v>2.7673551</v>
+        <v>3.074838999999999</v>
       </c>
       <c r="N11">
-        <v>44.0076449</v>
+        <v>43.700161</v>
       </c>
       <c r="O11">
-        <v>12.322140572</v>
+        <v>12.23604508</v>
       </c>
       <c r="P11">
-        <v>31.685504328</v>
+        <v>31.46411592</v>
       </c>
       <c r="Q11">
-        <v>54.785504328</v>
+        <v>54.56411592</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07205816679888308</v>
+        <v>0.07227366262817222</v>
       </c>
       <c r="T11">
-        <v>0.6064241754938356</v>
+        <v>0.6114009844843472</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.90242065429189</v>
+        <v>15.2121785888627</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.068667896365355</v>
+        <v>0.06850342094372641</v>
       </c>
       <c r="C12">
-        <v>474.8086906446255</v>
+        <v>471.9194184469658</v>
       </c>
       <c r="D12">
-        <v>535.1156906446255</v>
+        <v>538.3394184469659</v>
       </c>
       <c r="E12">
-        <v>-139.17</v>
+        <v>-133.057</v>
       </c>
       <c r="F12">
-        <v>61.13</v>
+        <v>67.24299999999999</v>
       </c>
       <c r="G12">
         <v>0.823</v>
@@ -2277,28 +2277,28 @@
         <v>46.775</v>
       </c>
       <c r="M12">
-        <v>3.074838999999999</v>
+        <v>3.3823229</v>
       </c>
       <c r="N12">
-        <v>43.700161</v>
+        <v>43.3926771</v>
       </c>
       <c r="O12">
-        <v>12.23604508</v>
+        <v>12.149949588</v>
       </c>
       <c r="P12">
-        <v>31.46411592</v>
+        <v>31.242727512</v>
       </c>
       <c r="Q12">
-        <v>54.56411592</v>
+        <v>54.342727512</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07227366262817222</v>
+        <v>0.07249400106036676</v>
       </c>
       <c r="T12">
-        <v>0.6114009844843472</v>
+        <v>0.61648963187914</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.2121785888627</v>
+        <v>13.82925326260246</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06850342094372641</v>
+        <v>0.06846854552209782</v>
       </c>
       <c r="C13">
-        <v>471.9194184469658</v>
+        <v>466.4949763127408</v>
       </c>
       <c r="D13">
-        <v>538.3394184469659</v>
+        <v>539.0279763127409</v>
       </c>
       <c r="E13">
-        <v>-133.057</v>
+        <v>-126.944</v>
       </c>
       <c r="F13">
-        <v>67.24299999999999</v>
+        <v>73.35599999999999</v>
       </c>
       <c r="G13">
         <v>0.823</v>
@@ -2359,45 +2359,45 @@
         <v>46.775</v>
       </c>
       <c r="M13">
-        <v>3.3823229</v>
+        <v>3.7998408</v>
       </c>
       <c r="N13">
-        <v>43.3926771</v>
+        <v>42.9751592</v>
       </c>
       <c r="O13">
-        <v>12.149949588</v>
+        <v>12.033044576</v>
       </c>
       <c r="P13">
-        <v>31.242727512</v>
+        <v>30.942114624</v>
       </c>
       <c r="Q13">
-        <v>54.342727512</v>
+        <v>54.042114624</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07249400106036676</v>
+        <v>0.07271934718420206</v>
       </c>
       <c r="T13">
-        <v>0.61648963187914</v>
+        <v>0.621693930351087</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.28</v>
       </c>
       <c r="W13">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.82925326260246</v>
+        <v>12.30972623905717</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06846854552209782</v>
+        <v>0.06831487010046923</v>
       </c>
       <c r="C14">
-        <v>466.4949763127408</v>
+        <v>463.4371444278117</v>
       </c>
       <c r="D14">
-        <v>539.0279763127409</v>
+        <v>542.0831444278117</v>
       </c>
       <c r="E14">
-        <v>-126.944</v>
+        <v>-120.831</v>
       </c>
       <c r="F14">
-        <v>73.35599999999999</v>
+        <v>79.46899999999999</v>
       </c>
       <c r="G14">
         <v>0.823</v>
@@ -2441,28 +2441,28 @@
         <v>46.775</v>
       </c>
       <c r="M14">
-        <v>3.7998408</v>
+        <v>4.1164942</v>
       </c>
       <c r="N14">
-        <v>42.9751592</v>
+        <v>42.6585058</v>
       </c>
       <c r="O14">
-        <v>12.033044576</v>
+        <v>11.944381624</v>
       </c>
       <c r="P14">
-        <v>30.942114624</v>
+        <v>30.714124176</v>
       </c>
       <c r="Q14">
-        <v>54.042114624</v>
+        <v>53.814124176</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07271934718420206</v>
+        <v>0.07294987367870026</v>
       </c>
       <c r="T14">
-        <v>0.621693930351087</v>
+        <v>0.6270178678683662</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.30972623905717</v>
+        <v>11.36282422066816</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06831487010046923</v>
+        <v>0.06816119467884063</v>
       </c>
       <c r="C15">
-        <v>463.4371444278117</v>
+        <v>460.4141428628864</v>
       </c>
       <c r="D15">
-        <v>542.0831444278117</v>
+        <v>545.1731428628864</v>
       </c>
       <c r="E15">
-        <v>-120.831</v>
+        <v>-114.718</v>
       </c>
       <c r="F15">
-        <v>79.46899999999999</v>
+        <v>85.58200000000001</v>
       </c>
       <c r="G15">
         <v>0.823</v>
@@ -2523,28 +2523,28 @@
         <v>46.775</v>
       </c>
       <c r="M15">
-        <v>4.1164942</v>
+        <v>4.433147600000001</v>
       </c>
       <c r="N15">
-        <v>42.6585058</v>
+        <v>42.3418524</v>
       </c>
       <c r="O15">
-        <v>11.944381624</v>
+        <v>11.855718672</v>
       </c>
       <c r="P15">
-        <v>30.714124176</v>
+        <v>30.486133728</v>
       </c>
       <c r="Q15">
-        <v>53.814124176</v>
+        <v>53.586133728</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07294987367870026</v>
+        <v>0.07318576125446585</v>
       </c>
       <c r="T15">
-        <v>0.6270178678683662</v>
+        <v>0.6324656178860473</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.36282422066816</v>
+        <v>10.55119391919186</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06816119467884063</v>
+        <v>0.06800751925721203</v>
       </c>
       <c r="C16">
-        <v>460.4141428628864</v>
+        <v>457.4265706550863</v>
       </c>
       <c r="D16">
-        <v>545.1731428628864</v>
+        <v>548.2985706550863</v>
       </c>
       <c r="E16">
-        <v>-114.718</v>
+        <v>-108.605</v>
       </c>
       <c r="F16">
-        <v>85.58200000000001</v>
+        <v>91.69500000000001</v>
       </c>
       <c r="G16">
         <v>0.823</v>
@@ -2605,28 +2605,28 @@
         <v>46.775</v>
       </c>
       <c r="M16">
-        <v>4.433147600000001</v>
+        <v>4.749801000000001</v>
       </c>
       <c r="N16">
-        <v>42.3418524</v>
+        <v>42.025199</v>
       </c>
       <c r="O16">
-        <v>11.855718672</v>
+        <v>11.76705572</v>
       </c>
       <c r="P16">
-        <v>30.486133728</v>
+        <v>30.25814328</v>
       </c>
       <c r="Q16">
-        <v>53.586133728</v>
+        <v>53.35814328</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07318576125446585</v>
+        <v>0.0734271991261318</v>
       </c>
       <c r="T16">
-        <v>0.6324656178860473</v>
+        <v>0.6380415502570855</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.55119391919186</v>
+        <v>9.847780991245738</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06800751925721202</v>
+        <v>0.06804968383558344</v>
       </c>
       <c r="C17">
-        <v>457.4265706550867</v>
+        <v>450.4524720474952</v>
       </c>
       <c r="D17">
-        <v>548.2985706550867</v>
+        <v>547.4374720474952</v>
       </c>
       <c r="E17">
-        <v>-108.605</v>
+        <v>-102.492</v>
       </c>
       <c r="F17">
-        <v>91.69499999999999</v>
+        <v>97.80799999999999</v>
       </c>
       <c r="G17">
         <v>0.823</v>
@@ -2687,45 +2687,45 @@
         <v>46.775</v>
       </c>
       <c r="M17">
-        <v>4.749801</v>
+        <v>5.232728</v>
       </c>
       <c r="N17">
-        <v>42.025199</v>
+        <v>41.542272</v>
       </c>
       <c r="O17">
-        <v>11.76705572</v>
+        <v>11.63183616</v>
       </c>
       <c r="P17">
-        <v>30.25814328</v>
+        <v>29.91043584</v>
       </c>
       <c r="Q17">
-        <v>53.35814328</v>
+        <v>53.01043584</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0734271991261318</v>
+        <v>0.07367438551855171</v>
       </c>
       <c r="T17">
-        <v>0.6380415502570855</v>
+        <v>0.6437502429226725</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.28</v>
       </c>
       <c r="W17">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.84778099124574</v>
+        <v>8.93893204462376</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06804968383558344</v>
+        <v>0.06790824841395483</v>
       </c>
       <c r="C18">
-        <v>450.4524720474952</v>
+        <v>447.2386484117844</v>
       </c>
       <c r="D18">
-        <v>547.4374720474952</v>
+        <v>550.3366484117844</v>
       </c>
       <c r="E18">
-        <v>-102.492</v>
+        <v>-96.379</v>
       </c>
       <c r="F18">
-        <v>97.80799999999999</v>
+        <v>103.921</v>
       </c>
       <c r="G18">
         <v>0.823</v>
@@ -2769,28 +2769,28 @@
         <v>46.775</v>
       </c>
       <c r="M18">
-        <v>5.232728</v>
+        <v>5.5597735</v>
       </c>
       <c r="N18">
-        <v>41.542272</v>
+        <v>41.2152265</v>
       </c>
       <c r="O18">
-        <v>11.63183616</v>
+        <v>11.54026342</v>
       </c>
       <c r="P18">
-        <v>29.91043584</v>
+        <v>29.67496308</v>
       </c>
       <c r="Q18">
-        <v>53.01043584</v>
+        <v>52.77496308</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07367438551855171</v>
+        <v>0.07392752820958415</v>
       </c>
       <c r="T18">
-        <v>0.6437502429226725</v>
+        <v>0.6495964944476709</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.93893204462376</v>
+        <v>8.413112512587068</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06790824841395483</v>
+        <v>0.06776681299232624</v>
       </c>
       <c r="C19">
-        <v>447.2386484117844</v>
+        <v>444.0556957860937</v>
       </c>
       <c r="D19">
-        <v>550.3366484117844</v>
+        <v>553.2666957860937</v>
       </c>
       <c r="E19">
-        <v>-96.379</v>
+        <v>-90.26600000000001</v>
       </c>
       <c r="F19">
-        <v>103.921</v>
+        <v>110.034</v>
       </c>
       <c r="G19">
         <v>0.823</v>
@@ -2851,28 +2851,28 @@
         <v>46.775</v>
       </c>
       <c r="M19">
-        <v>5.5597735</v>
+        <v>5.886819</v>
       </c>
       <c r="N19">
-        <v>41.2152265</v>
+        <v>40.888181</v>
       </c>
       <c r="O19">
-        <v>11.54026342</v>
+        <v>11.44869068</v>
       </c>
       <c r="P19">
-        <v>29.67496308</v>
+        <v>29.43949032</v>
       </c>
       <c r="Q19">
-        <v>52.77496308</v>
+        <v>52.53949032</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07392752820958415</v>
+        <v>0.07418684511259299</v>
       </c>
       <c r="T19">
-        <v>0.6495964944476709</v>
+        <v>0.6555853374732792</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.413112512587068</v>
+        <v>7.945717372998898</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06776681299232626</v>
+        <v>0.06773481757069766</v>
       </c>
       <c r="C20">
-        <v>444.0556957860933</v>
+        <v>438.6098615773106</v>
       </c>
       <c r="D20">
-        <v>553.2666957860934</v>
+        <v>553.9338615773106</v>
       </c>
       <c r="E20">
-        <v>-90.26600000000002</v>
+        <v>-84.15300000000002</v>
       </c>
       <c r="F20">
-        <v>110.034</v>
+        <v>116.147</v>
       </c>
       <c r="G20">
         <v>0.823</v>
@@ -2933,45 +2933,45 @@
         <v>46.775</v>
       </c>
       <c r="M20">
-        <v>5.886818999999999</v>
+        <v>6.3067821</v>
       </c>
       <c r="N20">
-        <v>40.888181</v>
+        <v>40.4682179</v>
       </c>
       <c r="O20">
-        <v>11.44869068</v>
+        <v>11.331101012</v>
       </c>
       <c r="P20">
-        <v>29.43949032</v>
+        <v>29.137116888</v>
       </c>
       <c r="Q20">
-        <v>52.53949032</v>
+        <v>52.237116888</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07418684511259299</v>
+        <v>0.07445256490209587</v>
       </c>
       <c r="T20">
-        <v>0.6555853374732792</v>
+        <v>0.6617220531661865</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.28</v>
       </c>
       <c r="W20">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.945717372998899</v>
+        <v>7.416619007655267</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06773481757069766</v>
+        <v>0.06759914214906906</v>
       </c>
       <c r="C21">
-        <v>438.6098615773106</v>
+        <v>435.343923616904</v>
       </c>
       <c r="D21">
-        <v>553.9338615773106</v>
+        <v>556.780923616904</v>
       </c>
       <c r="E21">
-        <v>-84.15300000000002</v>
+        <v>-78.04000000000002</v>
       </c>
       <c r="F21">
-        <v>116.147</v>
+        <v>122.26</v>
       </c>
       <c r="G21">
         <v>0.823</v>
@@ -3015,28 +3015,28 @@
         <v>46.775</v>
       </c>
       <c r="M21">
-        <v>6.3067821</v>
+        <v>6.638718</v>
       </c>
       <c r="N21">
-        <v>40.4682179</v>
+        <v>40.136282</v>
       </c>
       <c r="O21">
-        <v>11.331101012</v>
+        <v>11.23815896</v>
       </c>
       <c r="P21">
-        <v>29.137116888</v>
+        <v>28.89812304</v>
       </c>
       <c r="Q21">
-        <v>52.237116888</v>
+        <v>51.99812304</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07445256490209587</v>
+        <v>0.07472492768633632</v>
       </c>
       <c r="T21">
-        <v>0.6617220531661865</v>
+        <v>0.6680121867514163</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.416619007655267</v>
+        <v>7.045788057272504</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06759914214906906</v>
+        <v>0.06746346672744047</v>
       </c>
       <c r="C22">
-        <v>435.343923616904</v>
+        <v>432.1074030269157</v>
       </c>
       <c r="D22">
-        <v>556.780923616904</v>
+        <v>559.6574030269157</v>
       </c>
       <c r="E22">
-        <v>-78.04000000000002</v>
+        <v>-71.92700000000002</v>
       </c>
       <c r="F22">
-        <v>122.26</v>
+        <v>128.373</v>
       </c>
       <c r="G22">
         <v>0.823</v>
@@ -3097,28 +3097,28 @@
         <v>46.775</v>
       </c>
       <c r="M22">
-        <v>6.638718</v>
+        <v>6.970653899999999</v>
       </c>
       <c r="N22">
-        <v>40.136282</v>
+        <v>39.8043461</v>
       </c>
       <c r="O22">
-        <v>11.23815896</v>
+        <v>11.145216908</v>
       </c>
       <c r="P22">
-        <v>28.89812304</v>
+        <v>28.65912919199999</v>
       </c>
       <c r="Q22">
-        <v>51.99812304</v>
+        <v>51.759129192</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07472492768633632</v>
+        <v>0.0750041857309373</v>
       </c>
       <c r="T22">
-        <v>0.6680121867514163</v>
+        <v>0.6744615642248799</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.045788057272504</v>
+        <v>6.710274340259527</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06746346672744047</v>
+        <v>0.06732779130581187</v>
       </c>
       <c r="C23">
-        <v>432.1074030269157</v>
+        <v>428.9007581091043</v>
       </c>
       <c r="D23">
-        <v>559.6574030269157</v>
+        <v>562.5637581091044</v>
       </c>
       <c r="E23">
-        <v>-71.92700000000002</v>
+        <v>-65.81400000000002</v>
       </c>
       <c r="F23">
-        <v>128.373</v>
+        <v>134.486</v>
       </c>
       <c r="G23">
         <v>0.823</v>
@@ -3179,28 +3179,28 @@
         <v>46.775</v>
       </c>
       <c r="M23">
-        <v>6.970653899999999</v>
+        <v>7.3025898</v>
       </c>
       <c r="N23">
-        <v>39.8043461</v>
+        <v>39.4724102</v>
       </c>
       <c r="O23">
-        <v>11.145216908</v>
+        <v>11.052274856</v>
       </c>
       <c r="P23">
-        <v>28.65912919199999</v>
+        <v>28.420135344</v>
       </c>
       <c r="Q23">
-        <v>51.759129192</v>
+        <v>51.520135344</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0750041857309373</v>
+        <v>0.07529060423822034</v>
       </c>
       <c r="T23">
-        <v>0.6744615642248799</v>
+        <v>0.6810763103515093</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.710274340259527</v>
+        <v>6.40526187024773</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06732779130581187</v>
+        <v>0.06719211588418328</v>
       </c>
       <c r="C24">
-        <v>428.9007581091043</v>
+        <v>425.7244567349465</v>
       </c>
       <c r="D24">
-        <v>562.5637581091044</v>
+        <v>565.5004567349465</v>
       </c>
       <c r="E24">
-        <v>-65.81400000000002</v>
+        <v>-59.70100000000002</v>
       </c>
       <c r="F24">
-        <v>134.486</v>
+        <v>140.599</v>
       </c>
       <c r="G24">
         <v>0.823</v>
@@ -3261,28 +3261,28 @@
         <v>46.775</v>
       </c>
       <c r="M24">
-        <v>7.3025898</v>
+        <v>7.634525699999999</v>
       </c>
       <c r="N24">
-        <v>39.4724102</v>
+        <v>39.1404743</v>
       </c>
       <c r="O24">
-        <v>11.052274856</v>
+        <v>10.959332804</v>
       </c>
       <c r="P24">
-        <v>28.420135344</v>
+        <v>28.181141496</v>
       </c>
       <c r="Q24">
-        <v>51.520135344</v>
+        <v>51.281141496</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07529060423822034</v>
+        <v>0.07558446218725101</v>
       </c>
       <c r="T24">
-        <v>0.6810763103515093</v>
+        <v>0.6878628680658432</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.40526187024773</v>
+        <v>6.126772223715221</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06719211588418328</v>
+        <v>0.06722924046255468</v>
       </c>
       <c r="C25">
-        <v>425.7244567349465</v>
+        <v>418.804851495117</v>
       </c>
       <c r="D25">
-        <v>565.5004567349465</v>
+        <v>564.693851495117</v>
       </c>
       <c r="E25">
-        <v>-59.70100000000002</v>
+        <v>-53.58800000000002</v>
       </c>
       <c r="F25">
-        <v>140.599</v>
+        <v>146.712</v>
       </c>
       <c r="G25">
         <v>0.823</v>
@@ -3343,45 +3343,45 @@
         <v>46.775</v>
       </c>
       <c r="M25">
-        <v>7.634525699999999</v>
+        <v>8.1131736</v>
       </c>
       <c r="N25">
-        <v>39.1404743</v>
+        <v>38.6618264</v>
       </c>
       <c r="O25">
-        <v>10.959332804</v>
+        <v>10.825311392</v>
       </c>
       <c r="P25">
-        <v>28.181141496</v>
+        <v>27.836515008</v>
       </c>
       <c r="Q25">
-        <v>51.281141496</v>
+        <v>50.936515008</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07558446218725101</v>
+        <v>0.07588605324020353</v>
       </c>
       <c r="T25">
-        <v>0.6878628680658432</v>
+        <v>0.6948280194042387</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.28</v>
       </c>
       <c r="W25">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.126772223715221</v>
+        <v>5.765314820824245</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06722924046255468</v>
+        <v>0.06710076504092609</v>
       </c>
       <c r="C26">
-        <v>418.804851495117</v>
+        <v>415.4930810641993</v>
       </c>
       <c r="D26">
-        <v>564.693851495117</v>
+        <v>567.4950810641993</v>
       </c>
       <c r="E26">
-        <v>-53.58800000000002</v>
+        <v>-47.47500000000002</v>
       </c>
       <c r="F26">
-        <v>146.712</v>
+        <v>152.825</v>
       </c>
       <c r="G26">
         <v>0.823</v>
@@ -3425,28 +3425,28 @@
         <v>46.775</v>
       </c>
       <c r="M26">
-        <v>8.1131736</v>
+        <v>8.4512225</v>
       </c>
       <c r="N26">
-        <v>38.6618264</v>
+        <v>38.3237775</v>
       </c>
       <c r="O26">
-        <v>10.825311392</v>
+        <v>10.7306577</v>
       </c>
       <c r="P26">
-        <v>27.836515008</v>
+        <v>27.5931198</v>
       </c>
       <c r="Q26">
-        <v>50.936515008</v>
+        <v>50.6931198</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07588605324020353</v>
+        <v>0.07619568672123478</v>
       </c>
       <c r="T26">
-        <v>0.6948280194042387</v>
+        <v>0.7019789081116579</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.765314820824245</v>
+        <v>5.534702227991276</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06710076504092609</v>
+        <v>0.06697228961929749</v>
       </c>
       <c r="C27">
-        <v>415.4930810641993</v>
+        <v>412.2092408348628</v>
       </c>
       <c r="D27">
-        <v>567.4950810641993</v>
+        <v>570.3242408348628</v>
       </c>
       <c r="E27">
-        <v>-47.47500000000002</v>
+        <v>-41.36200000000002</v>
       </c>
       <c r="F27">
-        <v>152.825</v>
+        <v>158.938</v>
       </c>
       <c r="G27">
         <v>0.823</v>
@@ -3507,28 +3507,28 @@
         <v>46.775</v>
       </c>
       <c r="M27">
-        <v>8.4512225</v>
+        <v>8.789271400000001</v>
       </c>
       <c r="N27">
-        <v>38.3237775</v>
+        <v>37.9857286</v>
       </c>
       <c r="O27">
-        <v>10.7306577</v>
+        <v>10.636004008</v>
       </c>
       <c r="P27">
-        <v>27.5931198</v>
+        <v>27.349724592</v>
       </c>
       <c r="Q27">
-        <v>50.6931198</v>
+        <v>50.449724592</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07619568672123478</v>
+        <v>0.07651368867472634</v>
       </c>
       <c r="T27">
-        <v>0.7019789081116579</v>
+        <v>0.7093230640814399</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.534702227991276</v>
+        <v>5.321829065376226</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06697228961929749</v>
+        <v>0.06684381419766891</v>
       </c>
       <c r="C28">
-        <v>412.2092408348628</v>
+        <v>408.9537506252673</v>
       </c>
       <c r="D28">
-        <v>570.3242408348628</v>
+        <v>573.1817506252673</v>
       </c>
       <c r="E28">
-        <v>-41.36200000000002</v>
+        <v>-35.24900000000002</v>
       </c>
       <c r="F28">
-        <v>158.938</v>
+        <v>165.051</v>
       </c>
       <c r="G28">
         <v>0.823</v>
@@ -3589,28 +3589,28 @@
         <v>46.775</v>
       </c>
       <c r="M28">
-        <v>8.789271400000001</v>
+        <v>9.127320299999999</v>
       </c>
       <c r="N28">
-        <v>37.9857286</v>
+        <v>37.6476797</v>
       </c>
       <c r="O28">
-        <v>10.636004008</v>
+        <v>10.541350316</v>
       </c>
       <c r="P28">
-        <v>27.349724592</v>
+        <v>27.106329384</v>
       </c>
       <c r="Q28">
-        <v>50.449724592</v>
+        <v>50.206329384</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07651368867472634</v>
+        <v>0.07684040301050535</v>
       </c>
       <c r="T28">
-        <v>0.7093230640814399</v>
+        <v>0.7168684298038185</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.321829065376226</v>
+        <v>5.124724285177107</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06684381419766891</v>
+        <v>0.0667153387760403</v>
       </c>
       <c r="C29">
-        <v>408.9537506252673</v>
+        <v>405.7270387096431</v>
       </c>
       <c r="D29">
-        <v>573.1817506252673</v>
+        <v>576.0680387096431</v>
       </c>
       <c r="E29">
-        <v>-35.24900000000002</v>
+        <v>-29.136</v>
       </c>
       <c r="F29">
-        <v>165.051</v>
+        <v>171.164</v>
       </c>
       <c r="G29">
         <v>0.823</v>
@@ -3671,28 +3671,28 @@
         <v>46.775</v>
       </c>
       <c r="M29">
-        <v>9.127320299999999</v>
+        <v>9.465369200000001</v>
       </c>
       <c r="N29">
-        <v>37.6476797</v>
+        <v>37.30963079999999</v>
       </c>
       <c r="O29">
-        <v>10.541350316</v>
+        <v>10.446696624</v>
       </c>
       <c r="P29">
-        <v>27.106329384</v>
+        <v>26.862934176</v>
       </c>
       <c r="Q29">
-        <v>50.206329384</v>
+        <v>49.962934176</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07684040301050535</v>
+        <v>0.07717619274450042</v>
       </c>
       <c r="T29">
-        <v>0.7168684298038185</v>
+        <v>0.7246233890184856</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.124724285177107</v>
+        <v>4.941698417849352</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0667153387760403</v>
+        <v>0.06658686335441172</v>
       </c>
       <c r="C30">
-        <v>405.7270387096431</v>
+        <v>402.5295420322698</v>
       </c>
       <c r="D30">
-        <v>576.0680387096431</v>
+        <v>578.9835420322698</v>
       </c>
       <c r="E30">
-        <v>-29.136</v>
+        <v>-23.023</v>
       </c>
       <c r="F30">
-        <v>171.164</v>
+        <v>177.277</v>
       </c>
       <c r="G30">
         <v>0.823</v>
@@ -3753,28 +3753,28 @@
         <v>46.775</v>
       </c>
       <c r="M30">
-        <v>9.465369200000001</v>
+        <v>9.803418100000002</v>
       </c>
       <c r="N30">
-        <v>37.30963079999999</v>
+        <v>36.9715819</v>
       </c>
       <c r="O30">
-        <v>10.446696624</v>
+        <v>10.352042932</v>
       </c>
       <c r="P30">
-        <v>26.862934176</v>
+        <v>26.619538968</v>
       </c>
       <c r="Q30">
-        <v>49.962934176</v>
+        <v>49.71953896799999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07717619274450042</v>
+        <v>0.07752144134424185</v>
       </c>
       <c r="T30">
-        <v>0.7246233890184856</v>
+        <v>0.7325967977884953</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.941698417849352</v>
+        <v>4.771295024130409</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06658686335441172</v>
+        <v>0.06645838793278311</v>
       </c>
       <c r="C31">
-        <v>402.5295420322698</v>
+        <v>399.3617064279954</v>
       </c>
       <c r="D31">
-        <v>578.9835420322698</v>
+        <v>581.9287064279954</v>
       </c>
       <c r="E31">
-        <v>-23.02300000000002</v>
+        <v>-16.91000000000003</v>
       </c>
       <c r="F31">
-        <v>177.277</v>
+        <v>183.39</v>
       </c>
       <c r="G31">
         <v>0.823</v>
@@ -3835,28 +3835,28 @@
         <v>46.775</v>
       </c>
       <c r="M31">
-        <v>9.8034181</v>
+        <v>10.141467</v>
       </c>
       <c r="N31">
-        <v>36.9715819</v>
+        <v>36.633533</v>
       </c>
       <c r="O31">
-        <v>10.352042932</v>
+        <v>10.25738924</v>
       </c>
       <c r="P31">
-        <v>26.619538968</v>
+        <v>26.37614376</v>
       </c>
       <c r="Q31">
-        <v>49.71953896799999</v>
+        <v>49.47614376</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07752144134424185</v>
+        <v>0.07787655418969017</v>
       </c>
       <c r="T31">
-        <v>0.7325967977884953</v>
+        <v>0.7407980182376482</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.77129502413041</v>
+        <v>4.612251856659396</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06645838793278311</v>
+        <v>0.06688791251115452</v>
       </c>
       <c r="C32">
-        <v>399.3617064279954</v>
+        <v>383.5177079372812</v>
       </c>
       <c r="D32">
-        <v>581.9287064279954</v>
+        <v>572.1977079372812</v>
       </c>
       <c r="E32">
-        <v>-16.91000000000003</v>
+        <v>-10.79700000000003</v>
       </c>
       <c r="F32">
-        <v>183.39</v>
+        <v>189.503</v>
       </c>
       <c r="G32">
         <v>0.823</v>
@@ -3917,45 +3917,45 @@
         <v>46.775</v>
       </c>
       <c r="M32">
-        <v>10.141467</v>
+        <v>10.9532734</v>
       </c>
       <c r="N32">
-        <v>36.633533</v>
+        <v>35.8217266</v>
       </c>
       <c r="O32">
-        <v>10.25738924</v>
+        <v>10.030083448</v>
       </c>
       <c r="P32">
-        <v>26.37614376</v>
+        <v>25.791643152</v>
       </c>
       <c r="Q32">
-        <v>49.47614376</v>
+        <v>48.891643152</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07787655418969017</v>
+        <v>0.0782419601610935</v>
       </c>
       <c r="T32">
-        <v>0.7407980182376482</v>
+        <v>0.7492369552215591</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.28</v>
       </c>
       <c r="W32">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.612251856659396</v>
+        <v>4.270412897755295</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06688791251115452</v>
+        <v>0.06677743708952592</v>
       </c>
       <c r="C33">
-        <v>383.5177079372812</v>
+        <v>379.8763370167237</v>
       </c>
       <c r="D33">
-        <v>572.1977079372812</v>
+        <v>574.6693370167237</v>
       </c>
       <c r="E33">
-        <v>-10.79700000000003</v>
+        <v>-4.684000000000026</v>
       </c>
       <c r="F33">
-        <v>189.503</v>
+        <v>195.616</v>
       </c>
       <c r="G33">
         <v>0.823</v>
@@ -3999,28 +3999,28 @@
         <v>46.775</v>
       </c>
       <c r="M33">
-        <v>10.9532734</v>
+        <v>11.3066048</v>
       </c>
       <c r="N33">
-        <v>35.8217266</v>
+        <v>35.4683952</v>
       </c>
       <c r="O33">
-        <v>10.030083448</v>
+        <v>9.931150656</v>
       </c>
       <c r="P33">
-        <v>25.791643152</v>
+        <v>25.537244544</v>
       </c>
       <c r="Q33">
-        <v>48.891643152</v>
+        <v>48.637244544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0782419601610935</v>
+        <v>0.07861811336694989</v>
       </c>
       <c r="T33">
-        <v>0.7492369552215591</v>
+        <v>0.7579240962344086</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.270412897755295</v>
+        <v>4.136962494700443</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06677743708952592</v>
+        <v>0.06666696166789732</v>
       </c>
       <c r="C34">
-        <v>379.8763370167237</v>
+        <v>376.2564113153097</v>
       </c>
       <c r="D34">
-        <v>574.6693370167237</v>
+        <v>577.1624113153097</v>
       </c>
       <c r="E34">
-        <v>-4.684000000000026</v>
+        <v>1.428999999999974</v>
       </c>
       <c r="F34">
-        <v>195.616</v>
+        <v>201.729</v>
       </c>
       <c r="G34">
         <v>0.823</v>
@@ -4081,28 +4081,28 @@
         <v>46.775</v>
       </c>
       <c r="M34">
-        <v>11.3066048</v>
+        <v>11.6599362</v>
       </c>
       <c r="N34">
-        <v>35.4683952</v>
+        <v>35.1150638</v>
       </c>
       <c r="O34">
-        <v>9.931150656</v>
+        <v>9.832217864000002</v>
       </c>
       <c r="P34">
-        <v>25.537244544</v>
+        <v>25.282845936</v>
       </c>
       <c r="Q34">
-        <v>48.637244544</v>
+        <v>48.382845936</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07861811336694989</v>
+        <v>0.07900549502671243</v>
       </c>
       <c r="T34">
-        <v>0.7579240962344086</v>
+        <v>0.7668705548894327</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.136962494700443</v>
+        <v>4.011599994861035</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06666696166789732</v>
+        <v>0.06741328624626874</v>
       </c>
       <c r="C35">
-        <v>376.2564113153097</v>
+        <v>353.7098321617867</v>
       </c>
       <c r="D35">
-        <v>577.1624113153097</v>
+        <v>560.7288321617867</v>
       </c>
       <c r="E35">
-        <v>1.428999999999974</v>
+        <v>7.542000000000002</v>
       </c>
       <c r="F35">
-        <v>201.729</v>
+        <v>207.842</v>
       </c>
       <c r="G35">
         <v>0.823</v>
@@ -4163,45 +4163,45 @@
         <v>46.775</v>
       </c>
       <c r="M35">
-        <v>11.6599362</v>
+        <v>12.7407146</v>
       </c>
       <c r="N35">
-        <v>35.1150638</v>
+        <v>34.0342854</v>
       </c>
       <c r="O35">
-        <v>9.832217864000002</v>
+        <v>9.529599912000002</v>
       </c>
       <c r="P35">
-        <v>25.282845936</v>
+        <v>24.504685488</v>
       </c>
       <c r="Q35">
-        <v>48.382845936</v>
+        <v>47.604685488</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07900549502671243</v>
+        <v>0.07940461552464961</v>
       </c>
       <c r="T35">
-        <v>0.7668705548894327</v>
+        <v>0.7760881183521849</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.28</v>
       </c>
       <c r="W35">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.011599994861035</v>
+        <v>3.671301137221926</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06741328624626874</v>
+        <v>0.06732801082464013</v>
       </c>
       <c r="C36">
-        <v>353.7098321617867</v>
+        <v>349.4270313320652</v>
       </c>
       <c r="D36">
-        <v>560.7288321617867</v>
+        <v>562.5590313320653</v>
       </c>
       <c r="E36">
-        <v>7.542000000000002</v>
+        <v>13.655</v>
       </c>
       <c r="F36">
-        <v>207.842</v>
+        <v>213.955</v>
       </c>
       <c r="G36">
         <v>0.823</v>
@@ -4245,28 +4245,28 @@
         <v>46.775</v>
       </c>
       <c r="M36">
-        <v>12.7407146</v>
+        <v>13.1154415</v>
       </c>
       <c r="N36">
-        <v>34.0342854</v>
+        <v>33.6595585</v>
       </c>
       <c r="O36">
-        <v>9.529599912000002</v>
+        <v>9.424676379999999</v>
       </c>
       <c r="P36">
-        <v>24.504685488</v>
+        <v>24.23488211999999</v>
       </c>
       <c r="Q36">
-        <v>47.604685488</v>
+        <v>47.33488212</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07940461552464961</v>
+        <v>0.07981601665329252</v>
       </c>
       <c r="T36">
-        <v>0.7760881183521849</v>
+        <v>0.7855892991522524</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.671301137221926</v>
+        <v>3.566406819015585</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06732801082464013</v>
+        <v>0.06796849540301154</v>
       </c>
       <c r="C37">
-        <v>349.4270313320652</v>
+        <v>329.8529456937596</v>
       </c>
       <c r="D37">
-        <v>562.5590313320653</v>
+        <v>549.0979456937596</v>
       </c>
       <c r="E37">
-        <v>13.655</v>
+        <v>19.768</v>
       </c>
       <c r="F37">
-        <v>213.955</v>
+        <v>220.068</v>
       </c>
       <c r="G37">
         <v>0.823</v>
@@ -4327,45 +4327,45 @@
         <v>46.775</v>
       </c>
       <c r="M37">
-        <v>13.1154415</v>
+        <v>14.1063588</v>
       </c>
       <c r="N37">
-        <v>33.6595585</v>
+        <v>32.6686412</v>
       </c>
       <c r="O37">
-        <v>9.424676379999999</v>
+        <v>9.147219536</v>
       </c>
       <c r="P37">
-        <v>24.23488211999999</v>
+        <v>23.52142166399999</v>
       </c>
       <c r="Q37">
-        <v>47.33488212</v>
+        <v>46.621421664</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07981601665329252</v>
+        <v>0.08024027406720555</v>
       </c>
       <c r="T37">
-        <v>0.7855892991522524</v>
+        <v>0.795387391852322</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.28</v>
       </c>
       <c r="W37">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.566406819015585</v>
+        <v>3.315880494972238</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06796849540301156</v>
+        <v>0.06790337998138296</v>
       </c>
       <c r="C38">
-        <v>329.8529456937594</v>
+        <v>325.0789894741179</v>
       </c>
       <c r="D38">
-        <v>549.0979456937594</v>
+        <v>550.4369894741179</v>
       </c>
       <c r="E38">
-        <v>19.76799999999997</v>
+        <v>25.88099999999997</v>
       </c>
       <c r="F38">
-        <v>220.068</v>
+        <v>226.181</v>
       </c>
       <c r="G38">
         <v>0.823</v>
@@ -4409,28 +4409,28 @@
         <v>46.775</v>
       </c>
       <c r="M38">
-        <v>14.1063588</v>
+        <v>14.4982021</v>
       </c>
       <c r="N38">
-        <v>32.6686412</v>
+        <v>32.2767979</v>
       </c>
       <c r="O38">
-        <v>9.147219536</v>
+        <v>9.037503412</v>
       </c>
       <c r="P38">
-        <v>23.52142166399999</v>
+        <v>23.239294488</v>
       </c>
       <c r="Q38">
-        <v>46.621421664</v>
+        <v>46.339294488</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08024027406720555</v>
+        <v>0.08067799997044914</v>
       </c>
       <c r="T38">
-        <v>0.795387391852322</v>
+        <v>0.8054965351142986</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.315880494972239</v>
+        <v>3.226262103216233</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06790337998138296</v>
+        <v>0.06783826455975436</v>
       </c>
       <c r="C39">
-        <v>325.0789894741179</v>
+        <v>320.3115800700168</v>
       </c>
       <c r="D39">
-        <v>550.4369894741179</v>
+        <v>551.7825800700168</v>
       </c>
       <c r="E39">
-        <v>25.88099999999997</v>
+        <v>31.99399999999997</v>
       </c>
       <c r="F39">
-        <v>226.181</v>
+        <v>232.294</v>
       </c>
       <c r="G39">
         <v>0.823</v>
@@ -4491,28 +4491,28 @@
         <v>46.775</v>
       </c>
       <c r="M39">
-        <v>14.4982021</v>
+        <v>14.8900454</v>
       </c>
       <c r="N39">
-        <v>32.2767979</v>
+        <v>31.8849546</v>
       </c>
       <c r="O39">
-        <v>9.037503412</v>
+        <v>8.927787288000001</v>
       </c>
       <c r="P39">
-        <v>23.239294488</v>
+        <v>22.957167312</v>
       </c>
       <c r="Q39">
-        <v>46.339294488</v>
+        <v>46.057167312</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08067799997044914</v>
+        <v>0.08112984606411994</v>
       </c>
       <c r="T39">
-        <v>0.8054965351142986</v>
+        <v>0.815931779771823</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.226262103216233</v>
+        <v>3.141360468921069</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06783826455975436</v>
+        <v>0.06777314913812577</v>
       </c>
       <c r="C40">
-        <v>320.3115800700168</v>
+        <v>315.5507656118774</v>
       </c>
       <c r="D40">
-        <v>551.7825800700168</v>
+        <v>553.1347656118774</v>
       </c>
       <c r="E40">
-        <v>31.99399999999997</v>
+        <v>38.10699999999997</v>
       </c>
       <c r="F40">
-        <v>232.294</v>
+        <v>238.407</v>
       </c>
       <c r="G40">
         <v>0.823</v>
@@ -4573,28 +4573,28 @@
         <v>46.775</v>
       </c>
       <c r="M40">
-        <v>14.8900454</v>
+        <v>15.2818887</v>
       </c>
       <c r="N40">
-        <v>31.8849546</v>
+        <v>31.4931113</v>
       </c>
       <c r="O40">
-        <v>8.927787288000001</v>
+        <v>8.818071164000001</v>
       </c>
       <c r="P40">
-        <v>22.957167312</v>
+        <v>22.675040136</v>
       </c>
       <c r="Q40">
-        <v>46.057167312</v>
+        <v>45.775040136</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08112984606411994</v>
+        <v>0.08159650678381272</v>
       </c>
       <c r="T40">
-        <v>0.815931779771823</v>
+        <v>0.8267091635984464</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.141360468921069</v>
+        <v>3.060812764589759</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06777314913812577</v>
+        <v>0.06995443371649718</v>
       </c>
       <c r="C41">
-        <v>315.5507656118774</v>
+        <v>267.4750242916068</v>
       </c>
       <c r="D41">
-        <v>553.1347656118774</v>
+        <v>511.1720242916068</v>
       </c>
       <c r="E41">
-        <v>38.10699999999997</v>
+        <v>44.21999999999997</v>
       </c>
       <c r="F41">
-        <v>238.407</v>
+        <v>244.52</v>
       </c>
       <c r="G41">
         <v>0.823</v>
@@ -4655,45 +4655,45 @@
         <v>46.775</v>
       </c>
       <c r="M41">
-        <v>15.2818887</v>
+        <v>17.580988</v>
       </c>
       <c r="N41">
-        <v>31.4931113</v>
+        <v>29.194012</v>
       </c>
       <c r="O41">
-        <v>8.818071164000001</v>
+        <v>8.174323360000001</v>
       </c>
       <c r="P41">
-        <v>22.675040136</v>
+        <v>21.01968864</v>
       </c>
       <c r="Q41">
-        <v>45.775040136</v>
+        <v>44.11968864</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08159650678381272</v>
+        <v>0.08207872286082862</v>
       </c>
       <c r="T41">
-        <v>0.8267091635984464</v>
+        <v>0.8378457935526239</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.28</v>
       </c>
       <c r="W41">
-        <v>0.046152</v>
+        <v>0.051768</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.060812764589759</v>
+        <v>2.660544447217642</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06995443371649718</v>
+        <v>0.06994547829486858</v>
       </c>
       <c r="C42">
-        <v>267.4750242916068</v>
+        <v>261.5212851199257</v>
       </c>
       <c r="D42">
-        <v>511.1720242916068</v>
+        <v>511.3312851199257</v>
       </c>
       <c r="E42">
-        <v>44.21999999999997</v>
+        <v>50.333</v>
       </c>
       <c r="F42">
-        <v>244.52</v>
+        <v>250.633</v>
       </c>
       <c r="G42">
         <v>0.823</v>
@@ -4737,28 +4737,28 @@
         <v>46.775</v>
       </c>
       <c r="M42">
-        <v>17.580988</v>
+        <v>18.0205127</v>
       </c>
       <c r="N42">
-        <v>29.194012</v>
+        <v>28.7544873</v>
       </c>
       <c r="O42">
-        <v>8.174323360000001</v>
+        <v>8.051256444</v>
       </c>
       <c r="P42">
-        <v>21.01968864</v>
+        <v>20.703230856</v>
       </c>
       <c r="Q42">
-        <v>44.11968864</v>
+        <v>43.803230856</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08207872286082862</v>
+        <v>0.08257728524553995</v>
       </c>
       <c r="T42">
-        <v>0.8378457935526239</v>
+        <v>0.8493599363866041</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.660544447217642</v>
+        <v>2.595653119236724</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06994547829486858</v>
+        <v>0.06993652287323998</v>
       </c>
       <c r="C43">
-        <v>261.5212851199257</v>
+        <v>255.5676452178255</v>
       </c>
       <c r="D43">
-        <v>511.3312851199257</v>
+        <v>511.4906452178255</v>
       </c>
       <c r="E43">
-        <v>50.333</v>
+        <v>56.44599999999997</v>
       </c>
       <c r="F43">
-        <v>250.633</v>
+        <v>256.746</v>
       </c>
       <c r="G43">
         <v>0.823</v>
@@ -4819,28 +4819,28 @@
         <v>46.775</v>
       </c>
       <c r="M43">
-        <v>18.0205127</v>
+        <v>18.4600374</v>
       </c>
       <c r="N43">
-        <v>28.7544873</v>
+        <v>28.3149626</v>
       </c>
       <c r="O43">
-        <v>8.051256444</v>
+        <v>7.928189528</v>
       </c>
       <c r="P43">
-        <v>20.703230856</v>
+        <v>20.386773072</v>
       </c>
       <c r="Q43">
-        <v>43.803230856</v>
+        <v>43.486773072</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08257728524553995</v>
+        <v>0.08309303943662066</v>
       </c>
       <c r="T43">
-        <v>0.8493599363866041</v>
+        <v>0.8612711186286526</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.595653119236724</v>
+        <v>2.533851854492992</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06993652287324</v>
+        <v>0.07113500745161139</v>
       </c>
       <c r="C44">
-        <v>255.5676452178253</v>
+        <v>228.9753427711576</v>
       </c>
       <c r="D44">
-        <v>511.4906452178253</v>
+        <v>491.0113427711576</v>
       </c>
       <c r="E44">
-        <v>56.44599999999997</v>
+        <v>62.55899999999997</v>
       </c>
       <c r="F44">
-        <v>256.746</v>
+        <v>262.859</v>
       </c>
       <c r="G44">
         <v>0.823</v>
@@ -4901,45 +4901,45 @@
         <v>46.775</v>
       </c>
       <c r="M44">
-        <v>18.4600374</v>
+        <v>19.9247122</v>
       </c>
       <c r="N44">
-        <v>28.3149626</v>
+        <v>26.8502878</v>
       </c>
       <c r="O44">
-        <v>7.928189528</v>
+        <v>7.518080584</v>
       </c>
       <c r="P44">
-        <v>20.386773072</v>
+        <v>19.332207216</v>
       </c>
       <c r="Q44">
-        <v>43.486773072</v>
+        <v>42.43220721599999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08309303943662066</v>
+        <v>0.08362689026598488</v>
       </c>
       <c r="T44">
-        <v>0.8612711186286526</v>
+        <v>0.8736002370897202</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.28</v>
       </c>
       <c r="W44">
-        <v>0.051768</v>
+        <v>0.054576</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.533851854492992</v>
+        <v>2.347587233907449</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07113500745161139</v>
+        <v>0.07115413202998279</v>
       </c>
       <c r="C45">
-        <v>228.9753427711576</v>
+        <v>222.5488330411631</v>
       </c>
       <c r="D45">
-        <v>491.0113427711576</v>
+        <v>490.6978330411631</v>
       </c>
       <c r="E45">
-        <v>62.55899999999997</v>
+        <v>68.67199999999997</v>
       </c>
       <c r="F45">
-        <v>262.859</v>
+        <v>268.972</v>
       </c>
       <c r="G45">
         <v>0.823</v>
@@ -4983,28 +4983,28 @@
         <v>46.775</v>
       </c>
       <c r="M45">
-        <v>19.9247122</v>
+        <v>20.3880776</v>
       </c>
       <c r="N45">
-        <v>26.8502878</v>
+        <v>26.3869224</v>
       </c>
       <c r="O45">
-        <v>7.518080584</v>
+        <v>7.388338272</v>
       </c>
       <c r="P45">
-        <v>19.332207216</v>
+        <v>18.998584128</v>
       </c>
       <c r="Q45">
-        <v>42.43220721599999</v>
+        <v>42.098584128</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08362689026598488</v>
+        <v>0.08417980719639784</v>
       </c>
       <c r="T45">
-        <v>0.8736002370897202</v>
+        <v>0.8863696812101118</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.347587233907449</v>
+        <v>2.294232978591371</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07115413202998279</v>
+        <v>0.07117325660835419</v>
       </c>
       <c r="C46">
-        <v>222.5488330411631</v>
+        <v>216.1227234063412</v>
       </c>
       <c r="D46">
-        <v>490.6978330411631</v>
+        <v>490.3847234063412</v>
       </c>
       <c r="E46">
-        <v>68.67199999999997</v>
+        <v>74.78499999999997</v>
       </c>
       <c r="F46">
-        <v>268.972</v>
+        <v>275.085</v>
       </c>
       <c r="G46">
         <v>0.823</v>
@@ -5065,28 +5065,28 @@
         <v>46.775</v>
       </c>
       <c r="M46">
-        <v>20.3880776</v>
+        <v>20.851443</v>
       </c>
       <c r="N46">
-        <v>26.3869224</v>
+        <v>25.923557</v>
       </c>
       <c r="O46">
-        <v>7.388338272</v>
+        <v>7.25859596</v>
       </c>
       <c r="P46">
-        <v>18.998584128</v>
+        <v>18.66496104</v>
       </c>
       <c r="Q46">
-        <v>42.098584128</v>
+        <v>41.76496104</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08417980719639784</v>
+        <v>0.08475283019700762</v>
       </c>
       <c r="T46">
-        <v>0.8863696812101118</v>
+        <v>0.8996034687530629</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.294232978591371</v>
+        <v>2.243250023511562</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07117325660835419</v>
+        <v>0.07119238118672561</v>
       </c>
       <c r="C47">
-        <v>216.1227234063412</v>
+        <v>209.697013101289</v>
       </c>
       <c r="D47">
-        <v>490.3847234063412</v>
+        <v>490.072013101289</v>
       </c>
       <c r="E47">
-        <v>74.78499999999997</v>
+        <v>80.89799999999997</v>
       </c>
       <c r="F47">
-        <v>275.085</v>
+        <v>281.198</v>
       </c>
       <c r="G47">
         <v>0.823</v>
@@ -5147,28 +5147,28 @@
         <v>46.775</v>
       </c>
       <c r="M47">
-        <v>20.851443</v>
+        <v>21.3148084</v>
       </c>
       <c r="N47">
-        <v>25.923557</v>
+        <v>25.4601916</v>
       </c>
       <c r="O47">
-        <v>7.25859596</v>
+        <v>7.128853648</v>
       </c>
       <c r="P47">
-        <v>18.66496104</v>
+        <v>18.331337952</v>
       </c>
       <c r="Q47">
-        <v>41.76496104</v>
+        <v>41.431337952</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08475283019700762</v>
+        <v>0.08534707627171406</v>
       </c>
       <c r="T47">
-        <v>0.8996034687530629</v>
+        <v>0.9133273965753828</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.243250023511562</v>
+        <v>2.194483718652615</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07119238118672561</v>
+        <v>0.07121150576509701</v>
       </c>
       <c r="C48">
-        <v>209.697013101289</v>
+        <v>203.2717013625559</v>
       </c>
       <c r="D48">
-        <v>490.072013101289</v>
+        <v>489.7597013625559</v>
       </c>
       <c r="E48">
-        <v>80.89799999999997</v>
+        <v>87.01099999999997</v>
       </c>
       <c r="F48">
-        <v>281.198</v>
+        <v>287.311</v>
       </c>
       <c r="G48">
         <v>0.823</v>
@@ -5229,28 +5229,28 @@
         <v>46.775</v>
       </c>
       <c r="M48">
-        <v>21.3148084</v>
+        <v>21.7781738</v>
       </c>
       <c r="N48">
-        <v>25.4601916</v>
+        <v>24.9968262</v>
       </c>
       <c r="O48">
-        <v>7.128853648</v>
+        <v>6.999111336</v>
       </c>
       <c r="P48">
-        <v>18.331337952</v>
+        <v>17.997714864</v>
       </c>
       <c r="Q48">
-        <v>41.431337952</v>
+        <v>41.097714864</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08534707627171406</v>
+        <v>0.08596374672659812</v>
       </c>
       <c r="T48">
-        <v>0.9133273965753828</v>
+        <v>0.9275692084664694</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.194483718652615</v>
+        <v>2.147792575702559</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07121150576509701</v>
+        <v>0.07123063034346841</v>
       </c>
       <c r="C49">
-        <v>203.2717013625559</v>
+        <v>196.846787428635</v>
       </c>
       <c r="D49">
-        <v>489.7597013625559</v>
+        <v>489.447787428635</v>
       </c>
       <c r="E49">
-        <v>87.01099999999997</v>
+        <v>93.12399999999997</v>
       </c>
       <c r="F49">
-        <v>287.311</v>
+        <v>293.424</v>
       </c>
       <c r="G49">
         <v>0.823</v>
@@ -5311,28 +5311,28 @@
         <v>46.775</v>
       </c>
       <c r="M49">
-        <v>21.7781738</v>
+        <v>22.2415392</v>
       </c>
       <c r="N49">
-        <v>24.9968262</v>
+        <v>24.5334608</v>
       </c>
       <c r="O49">
-        <v>6.999111336</v>
+        <v>6.869369024</v>
       </c>
       <c r="P49">
-        <v>17.997714864</v>
+        <v>17.664091776</v>
       </c>
       <c r="Q49">
-        <v>41.097714864</v>
+        <v>40.764091776</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08596374672659812</v>
+        <v>0.08660413527590079</v>
       </c>
       <c r="T49">
-        <v>0.9275692084664694</v>
+        <v>0.942358782353367</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.147792575702559</v>
+        <v>2.103046897042089</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07123063034346841</v>
+        <v>0.07124975492183983</v>
       </c>
       <c r="C50">
-        <v>196.846787428635</v>
+        <v>190.4222705399584</v>
       </c>
       <c r="D50">
-        <v>489.447787428635</v>
+        <v>489.1362705399584</v>
       </c>
       <c r="E50">
-        <v>93.12399999999997</v>
+        <v>99.23699999999997</v>
       </c>
       <c r="F50">
-        <v>293.424</v>
+        <v>299.537</v>
       </c>
       <c r="G50">
         <v>0.823</v>
@@ -5393,28 +5393,28 @@
         <v>46.775</v>
       </c>
       <c r="M50">
-        <v>22.2415392</v>
+        <v>22.7049046</v>
       </c>
       <c r="N50">
-        <v>24.5334608</v>
+        <v>24.0700954</v>
       </c>
       <c r="O50">
-        <v>6.869369024</v>
+        <v>6.739626712000001</v>
       </c>
       <c r="P50">
-        <v>17.664091776</v>
+        <v>17.330468688</v>
       </c>
       <c r="Q50">
-        <v>40.764091776</v>
+        <v>40.430468688</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08660413527590079</v>
+        <v>0.0872696371016467</v>
       </c>
       <c r="T50">
-        <v>0.9423587823533669</v>
+        <v>0.9577283395299468</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.103046897042089</v>
+        <v>2.060127572612659</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07124975492183983</v>
+        <v>0.07126887950021121</v>
       </c>
       <c r="C51">
-        <v>190.4222705399584</v>
+        <v>183.9981499388917</v>
       </c>
       <c r="D51">
-        <v>489.1362705399584</v>
+        <v>488.8251499388917</v>
       </c>
       <c r="E51">
-        <v>99.23699999999997</v>
+        <v>105.35</v>
       </c>
       <c r="F51">
-        <v>299.537</v>
+        <v>305.65</v>
       </c>
       <c r="G51">
         <v>0.823</v>
@@ -5475,28 +5475,28 @@
         <v>46.775</v>
       </c>
       <c r="M51">
-        <v>22.7049046</v>
+        <v>23.16827</v>
       </c>
       <c r="N51">
-        <v>24.0700954</v>
+        <v>23.60673</v>
       </c>
       <c r="O51">
-        <v>6.739626712000001</v>
+        <v>6.6098844</v>
       </c>
       <c r="P51">
-        <v>17.330468688</v>
+        <v>16.9968456</v>
       </c>
       <c r="Q51">
-        <v>40.430468688</v>
+        <v>40.0968456</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0872696371016467</v>
+        <v>0.08796175900042244</v>
       </c>
       <c r="T51">
-        <v>0.9577283395299468</v>
+        <v>0.9737126789935899</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.060127572612659</v>
+        <v>2.018925021160406</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07126887950021121</v>
+        <v>0.07650224407858264</v>
       </c>
       <c r="C52">
-        <v>183.9981499388917</v>
+        <v>105.416045052312</v>
       </c>
       <c r="D52">
-        <v>488.8251499388917</v>
+        <v>416.356045052312</v>
       </c>
       <c r="E52">
-        <v>105.35</v>
+        <v>111.463</v>
       </c>
       <c r="F52">
-        <v>305.65</v>
+        <v>311.763</v>
       </c>
       <c r="G52">
         <v>0.823</v>
@@ -5557,45 +5557,45 @@
         <v>46.775</v>
       </c>
       <c r="M52">
-        <v>23.16827</v>
+        <v>28.05867</v>
       </c>
       <c r="N52">
-        <v>23.60673</v>
+        <v>18.71633</v>
       </c>
       <c r="O52">
-        <v>6.6098844</v>
+        <v>5.240572400000001</v>
       </c>
       <c r="P52">
-        <v>16.9968456</v>
+        <v>13.4757576</v>
       </c>
       <c r="Q52">
-        <v>40.0968456</v>
+        <v>36.5757576</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08796175900042244</v>
+        <v>0.08868213077261761</v>
       </c>
       <c r="T52">
-        <v>0.9737126789935899</v>
+        <v>0.9903494404761573</v>
       </c>
       <c r="U52">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V52">
         <v>0.28</v>
       </c>
       <c r="W52">
-        <v>0.054576</v>
+        <v>0.0648</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.018925021160406</v>
+        <v>1.667042664531142</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07650224407858264</v>
+        <v>0.07662360865695403</v>
       </c>
       <c r="C53">
-        <v>105.416045052312</v>
+        <v>97.87650282608161</v>
       </c>
       <c r="D53">
-        <v>416.356045052312</v>
+        <v>414.9295028260816</v>
       </c>
       <c r="E53">
-        <v>111.463</v>
+        <v>117.576</v>
       </c>
       <c r="F53">
-        <v>311.763</v>
+        <v>317.876</v>
       </c>
       <c r="G53">
         <v>0.823</v>
@@ -5639,28 +5639,28 @@
         <v>46.775</v>
       </c>
       <c r="M53">
-        <v>28.05867</v>
+        <v>28.60884</v>
       </c>
       <c r="N53">
-        <v>18.71633</v>
+        <v>18.16616</v>
       </c>
       <c r="O53">
-        <v>5.240572400000001</v>
+        <v>5.086524800000001</v>
       </c>
       <c r="P53">
-        <v>13.4757576</v>
+        <v>13.0796352</v>
       </c>
       <c r="Q53">
-        <v>36.5757576</v>
+        <v>36.1796352</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08868213077261761</v>
+        <v>0.0894325180353209</v>
       </c>
       <c r="T53">
-        <v>0.9903494404761573</v>
+        <v>1.007679400353831</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.667042664531142</v>
+        <v>1.634984151751696</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07662360865695403</v>
+        <v>0.07674497323532543</v>
       </c>
       <c r="C54">
-        <v>97.87650282608161</v>
+        <v>90.34670261775796</v>
       </c>
       <c r="D54">
-        <v>414.9295028260816</v>
+        <v>413.512702617758</v>
       </c>
       <c r="E54">
-        <v>117.576</v>
+        <v>123.689</v>
       </c>
       <c r="F54">
-        <v>317.876</v>
+        <v>323.989</v>
       </c>
       <c r="G54">
         <v>0.823</v>
@@ -5721,28 +5721,28 @@
         <v>46.775</v>
       </c>
       <c r="M54">
-        <v>28.60884</v>
+        <v>29.15900999999999</v>
       </c>
       <c r="N54">
-        <v>18.16616</v>
+        <v>17.61599</v>
       </c>
       <c r="O54">
-        <v>5.086524800000001</v>
+        <v>4.932477200000002</v>
       </c>
       <c r="P54">
-        <v>13.0796352</v>
+        <v>12.6835128</v>
       </c>
       <c r="Q54">
-        <v>36.1796352</v>
+        <v>35.7835128</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.0894325180353209</v>
+        <v>0.09021483667090519</v>
       </c>
       <c r="T54">
-        <v>1.007679400353831</v>
+        <v>1.025746805332683</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.634984151751696</v>
+        <v>1.604135394171476</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07674497323532543</v>
+        <v>0.07686633781369684</v>
       </c>
       <c r="C55">
-        <v>90.34670261775796</v>
+        <v>82.82654497292373</v>
       </c>
       <c r="D55">
-        <v>413.512702617758</v>
+        <v>412.1055449729237</v>
       </c>
       <c r="E55">
-        <v>123.689</v>
+        <v>129.802</v>
       </c>
       <c r="F55">
-        <v>323.989</v>
+        <v>330.102</v>
       </c>
       <c r="G55">
         <v>0.823</v>
@@ -5803,28 +5803,28 @@
         <v>46.775</v>
       </c>
       <c r="M55">
-        <v>29.15900999999999</v>
+        <v>29.70918</v>
       </c>
       <c r="N55">
-        <v>17.61599</v>
+        <v>17.06582</v>
       </c>
       <c r="O55">
-        <v>4.932477200000002</v>
+        <v>4.778429600000001</v>
       </c>
       <c r="P55">
-        <v>12.6835128</v>
+        <v>12.2873904</v>
       </c>
       <c r="Q55">
-        <v>35.7835128</v>
+        <v>35.3873904</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09021483667090519</v>
+        <v>0.09103116916021053</v>
       </c>
       <c r="T55">
-        <v>1.025746805332683</v>
+        <v>1.044599749658442</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.604135394171476</v>
+        <v>1.5744291831683</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07686633781369684</v>
+        <v>0.07698770239206826</v>
       </c>
       <c r="C56">
-        <v>82.82654497292373</v>
+        <v>75.31593178631874</v>
       </c>
       <c r="D56">
-        <v>412.1055449729237</v>
+        <v>410.7079317863187</v>
       </c>
       <c r="E56">
-        <v>129.802</v>
+        <v>135.915</v>
       </c>
       <c r="F56">
-        <v>330.102</v>
+        <v>336.215</v>
       </c>
       <c r="G56">
         <v>0.823</v>
@@ -5885,28 +5885,28 @@
         <v>46.775</v>
       </c>
       <c r="M56">
-        <v>29.70918</v>
+        <v>30.25935</v>
       </c>
       <c r="N56">
-        <v>17.06582</v>
+        <v>16.51565</v>
       </c>
       <c r="O56">
-        <v>4.778429600000001</v>
+        <v>4.624382000000001</v>
       </c>
       <c r="P56">
-        <v>12.2873904</v>
+        <v>11.891268</v>
       </c>
       <c r="Q56">
-        <v>35.3873904</v>
+        <v>34.99126800000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09103116916021053</v>
+        <v>0.09188378309348501</v>
       </c>
       <c r="T56">
-        <v>1.044599749658442</v>
+        <v>1.064290602620901</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.5744291831683</v>
+        <v>1.545803198019786</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07698770239206826</v>
+        <v>0.07710906697043965</v>
       </c>
       <c r="C57">
-        <v>75.31593178631874</v>
+        <v>67.81476627904044</v>
       </c>
       <c r="D57">
-        <v>410.7079317863187</v>
+        <v>409.3197662790405</v>
       </c>
       <c r="E57">
-        <v>135.915</v>
+        <v>142.028</v>
       </c>
       <c r="F57">
-        <v>336.215</v>
+        <v>342.328</v>
       </c>
       <c r="G57">
         <v>0.823</v>
@@ -5967,28 +5967,28 @@
         <v>46.775</v>
       </c>
       <c r="M57">
-        <v>30.25935</v>
+        <v>30.80952</v>
       </c>
       <c r="N57">
-        <v>16.51565</v>
+        <v>15.96548</v>
       </c>
       <c r="O57">
-        <v>4.624382000000001</v>
+        <v>4.4703344</v>
       </c>
       <c r="P57">
-        <v>11.891268</v>
+        <v>11.4951456</v>
       </c>
       <c r="Q57">
-        <v>34.99126800000001</v>
+        <v>34.5951456</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09188378309348501</v>
+        <v>0.09277515220554466</v>
       </c>
       <c r="T57">
-        <v>1.064290602620901</v>
+        <v>1.08487649435438</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.545803198019786</v>
+        <v>1.518199569483718</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07710906697043965</v>
+        <v>0.1028803017138848</v>
       </c>
       <c r="C58">
-        <v>67.81476627904044</v>
+        <v>-109.3246869893404</v>
       </c>
       <c r="D58">
-        <v>409.3197662790405</v>
+        <v>238.2933130106597</v>
       </c>
       <c r="E58">
-        <v>142.028</v>
+        <v>148.141</v>
       </c>
       <c r="F58">
-        <v>342.328</v>
+        <v>348.441</v>
       </c>
       <c r="G58">
         <v>0.823</v>
@@ -6049,45 +6049,45 @@
         <v>46.775</v>
       </c>
       <c r="M58">
-        <v>30.80952</v>
+        <v>51.15113880000001</v>
       </c>
       <c r="N58">
-        <v>15.96548</v>
+        <v>-4.376138800000014</v>
       </c>
       <c r="O58">
-        <v>4.4703344</v>
+        <v>-1.225318864000004</v>
       </c>
       <c r="P58">
-        <v>11.4951456</v>
+        <v>-3.15081993600001</v>
       </c>
       <c r="Q58">
-        <v>34.5951456</v>
+        <v>19.94918006399999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09277515220554466</v>
+        <v>0.09448635822892795</v>
       </c>
       <c r="T58">
-        <v>1.08487649435438</v>
+        <v>1.124396263947528</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.28</v>
+        <v>0.2560451303187798</v>
       </c>
       <c r="W58">
-        <v>0.0648</v>
+        <v>0.1092125748692031</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.518199569483718</v>
+        <v>0.9144468939956423</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1028803017138848</v>
+        <v>0.1038903017138848</v>
       </c>
       <c r="C59">
-        <v>-109.3246869893404</v>
+        <v>-119.2769203706243</v>
       </c>
       <c r="D59">
-        <v>238.2933130106597</v>
+        <v>234.4540796293757</v>
       </c>
       <c r="E59">
-        <v>148.141</v>
+        <v>154.254</v>
       </c>
       <c r="F59">
-        <v>348.441</v>
+        <v>354.554</v>
       </c>
       <c r="G59">
         <v>0.823</v>
@@ -6131,37 +6131,37 @@
         <v>46.775</v>
       </c>
       <c r="M59">
-        <v>51.15113880000001</v>
+        <v>52.04852720000001</v>
       </c>
       <c r="N59">
-        <v>-4.376138800000014</v>
+        <v>-5.273527200000011</v>
       </c>
       <c r="O59">
-        <v>-1.225318864000004</v>
+        <v>-1.476587616000003</v>
       </c>
       <c r="P59">
-        <v>-3.15081993600001</v>
+        <v>-3.796939584000008</v>
       </c>
       <c r="Q59">
-        <v>19.94918006399999</v>
+        <v>19.30306041599999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09448635822892795</v>
+        <v>0.09564555723437862</v>
       </c>
       <c r="T59">
-        <v>1.124396263947528</v>
+        <v>1.151167603565326</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2560451303187798</v>
+        <v>0.2516305591063872</v>
       </c>
       <c r="W59">
-        <v>0.1092125748692031</v>
+        <v>0.1098606339231824</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9144468939956423</v>
+        <v>0.8986805682370969</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1038903017138848</v>
+        <v>0.1049003017138848</v>
       </c>
       <c r="C60">
-        <v>-119.2769203706242</v>
+        <v>-129.1074046258564</v>
       </c>
       <c r="D60">
-        <v>234.4540796293758</v>
+        <v>230.7365953741436</v>
       </c>
       <c r="E60">
-        <v>154.254</v>
+        <v>160.367</v>
       </c>
       <c r="F60">
-        <v>354.554</v>
+        <v>360.667</v>
       </c>
       <c r="G60">
         <v>0.823</v>
@@ -6213,37 +6213,37 @@
         <v>46.775</v>
       </c>
       <c r="M60">
-        <v>52.0485272</v>
+        <v>52.9459156</v>
       </c>
       <c r="N60">
-        <v>-5.273527200000004</v>
+        <v>-6.170915600000001</v>
       </c>
       <c r="O60">
-        <v>-1.476587616000001</v>
+        <v>-1.727856368</v>
       </c>
       <c r="P60">
-        <v>-3.796939584000003</v>
+        <v>-4.443059232</v>
       </c>
       <c r="Q60">
-        <v>19.303060416</v>
+        <v>18.656940768</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09564555723437861</v>
+        <v>0.09686130253277811</v>
       </c>
       <c r="T60">
-        <v>1.151167603565326</v>
+        <v>1.179244862188871</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2516305591063872</v>
+        <v>0.2473656343757705</v>
       </c>
       <c r="W60">
-        <v>0.1098606339231824</v>
+        <v>0.1104867248736369</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.898680568237097</v>
+        <v>0.8834486941991802</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1049003017138848</v>
+        <v>0.1059103017138848</v>
       </c>
       <c r="C61">
-        <v>-129.1074046258564</v>
+        <v>-138.8218406932822</v>
       </c>
       <c r="D61">
-        <v>230.7365953741436</v>
+        <v>227.1351593067177</v>
       </c>
       <c r="E61">
-        <v>160.367</v>
+        <v>166.48</v>
       </c>
       <c r="F61">
-        <v>360.667</v>
+        <v>366.78</v>
       </c>
       <c r="G61">
         <v>0.823</v>
@@ -6295,37 +6295,37 @@
         <v>46.775</v>
       </c>
       <c r="M61">
-        <v>52.9459156</v>
+        <v>53.843304</v>
       </c>
       <c r="N61">
-        <v>-6.170915600000001</v>
+        <v>-7.068304000000005</v>
       </c>
       <c r="O61">
-        <v>-1.727856368</v>
+        <v>-1.979125120000002</v>
       </c>
       <c r="P61">
-        <v>-4.443059232</v>
+        <v>-5.089178880000003</v>
       </c>
       <c r="Q61">
-        <v>18.656940768</v>
+        <v>18.01082112</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09686130253277811</v>
+        <v>0.09813783509609755</v>
       </c>
       <c r="T61">
-        <v>1.179244862188871</v>
+        <v>1.208725983743592</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2473656343757705</v>
+        <v>0.2432428738028409</v>
       </c>
       <c r="W61">
-        <v>0.1104867248736369</v>
+        <v>0.111091946125743</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8834486941991802</v>
+        <v>0.8687245492958604</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1059103017138848</v>
+        <v>0.1069203017138848</v>
       </c>
       <c r="C62">
-        <v>-138.8218406932822</v>
+        <v>-148.4255790504988</v>
       </c>
       <c r="D62">
-        <v>227.1351593067177</v>
+        <v>223.6444209495011</v>
       </c>
       <c r="E62">
-        <v>166.48</v>
+        <v>172.593</v>
       </c>
       <c r="F62">
-        <v>366.78</v>
+        <v>372.893</v>
       </c>
       <c r="G62">
         <v>0.823</v>
@@ -6377,37 +6377,37 @@
         <v>46.775</v>
       </c>
       <c r="M62">
-        <v>53.843304</v>
+        <v>54.7406924</v>
       </c>
       <c r="N62">
-        <v>-7.068304000000005</v>
+        <v>-7.965692400000002</v>
       </c>
       <c r="O62">
-        <v>-1.979125120000002</v>
+        <v>-2.230393872</v>
       </c>
       <c r="P62">
-        <v>-5.089178880000003</v>
+        <v>-5.735298528000001</v>
       </c>
       <c r="Q62">
-        <v>18.01082112</v>
+        <v>17.364701472</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09813783509609755</v>
+        <v>0.09947983086779236</v>
       </c>
       <c r="T62">
-        <v>1.208725983743592</v>
+        <v>1.239718957685736</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2432428738028409</v>
+        <v>0.2392552857077124</v>
       </c>
       <c r="W62">
-        <v>0.111091946125743</v>
+        <v>0.1116773240581078</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8687245492958604</v>
+        <v>0.8544831632418299</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1069203017138848</v>
+        <v>0.1079303017138848</v>
       </c>
       <c r="C63">
-        <v>-148.4255790504988</v>
+        <v>-157.9236462372011</v>
       </c>
       <c r="D63">
-        <v>223.6444209495011</v>
+        <v>220.2593537627989</v>
       </c>
       <c r="E63">
-        <v>172.593</v>
+        <v>178.706</v>
       </c>
       <c r="F63">
-        <v>372.893</v>
+        <v>379.006</v>
       </c>
       <c r="G63">
         <v>0.823</v>
@@ -6459,37 +6459,37 @@
         <v>46.775</v>
       </c>
       <c r="M63">
-        <v>54.7406924</v>
+        <v>55.6380808</v>
       </c>
       <c r="N63">
-        <v>-7.965692400000002</v>
+        <v>-8.863080800000006</v>
       </c>
       <c r="O63">
-        <v>-2.230393872</v>
+        <v>-2.481662624000002</v>
       </c>
       <c r="P63">
-        <v>-5.735298528000001</v>
+        <v>-6.381418176000004</v>
       </c>
       <c r="Q63">
-        <v>17.364701472</v>
+        <v>16.718581824</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09947983086779236</v>
+        <v>0.1008924579958922</v>
       </c>
       <c r="T63">
-        <v>1.239718957685736</v>
+        <v>1.272343140782729</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2392552857077124</v>
+        <v>0.2353963294866202</v>
       </c>
       <c r="W63">
-        <v>0.1116773240581078</v>
+        <v>0.1122438188313642</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8544831632418299</v>
+        <v>0.8407011767379293</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1079303017138848</v>
+        <v>0.1089403017138848</v>
       </c>
       <c r="C64">
-        <v>-157.9236462372011</v>
+        <v>-167.3207690051622</v>
       </c>
       <c r="D64">
-        <v>220.2593537627989</v>
+        <v>216.9752309948377</v>
       </c>
       <c r="E64">
-        <v>178.706</v>
+        <v>184.819</v>
       </c>
       <c r="F64">
-        <v>379.006</v>
+        <v>385.119</v>
       </c>
       <c r="G64">
         <v>0.823</v>
@@ -6541,37 +6541,37 @@
         <v>46.775</v>
       </c>
       <c r="M64">
-        <v>55.6380808</v>
+        <v>56.5354692</v>
       </c>
       <c r="N64">
-        <v>-8.863080800000006</v>
+        <v>-9.760469200000003</v>
       </c>
       <c r="O64">
-        <v>-2.481662624000002</v>
+        <v>-2.732931376000001</v>
       </c>
       <c r="P64">
-        <v>-6.381418176000004</v>
+        <v>-7.027537824000001</v>
       </c>
       <c r="Q64">
-        <v>16.718581824</v>
+        <v>16.072462176</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1008924579958922</v>
+        <v>0.1023814433471325</v>
       </c>
       <c r="T64">
-        <v>1.272343140782729</v>
+        <v>1.306730793236316</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2353963294866202</v>
+        <v>0.2316598798122295</v>
       </c>
       <c r="W64">
-        <v>0.1122438188313642</v>
+        <v>0.1127923296435647</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8407011767379293</v>
+        <v>0.8273567136151052</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1089403017138848</v>
+        <v>0.1099503017138848</v>
       </c>
       <c r="C65">
-        <v>-167.3207690051622</v>
+        <v>-176.6213963394617</v>
       </c>
       <c r="D65">
-        <v>216.9752309948377</v>
+        <v>213.7876036605382</v>
       </c>
       <c r="E65">
-        <v>184.819</v>
+        <v>190.932</v>
       </c>
       <c r="F65">
-        <v>385.119</v>
+        <v>391.232</v>
       </c>
       <c r="G65">
         <v>0.823</v>
@@ -6623,37 +6623,37 @@
         <v>46.775</v>
       </c>
       <c r="M65">
-        <v>56.5354692</v>
+        <v>57.4328576</v>
       </c>
       <c r="N65">
-        <v>-9.760469200000003</v>
+        <v>-10.6578576</v>
       </c>
       <c r="O65">
-        <v>-2.732931376000001</v>
+        <v>-2.984200128</v>
       </c>
       <c r="P65">
-        <v>-7.027537824000001</v>
+        <v>-7.673657471999999</v>
       </c>
       <c r="Q65">
-        <v>16.072462176</v>
+        <v>15.426342528</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1023814433471325</v>
+        <v>0.1039531501067751</v>
       </c>
       <c r="T65">
-        <v>1.306730793236316</v>
+        <v>1.343028870826214</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2316598798122295</v>
+        <v>0.2280401941901634</v>
       </c>
       <c r="W65">
-        <v>0.1127923296435647</v>
+        <v>0.113323699492884</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8273567136151052</v>
+        <v>0.8144292649648692</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1099503017138848</v>
+        <v>0.1109603017138848</v>
       </c>
       <c r="C66">
-        <v>-176.6213963394617</v>
+        <v>-185.8297195667062</v>
       </c>
       <c r="D66">
-        <v>213.7876036605382</v>
+        <v>210.6922804332937</v>
       </c>
       <c r="E66">
-        <v>190.932</v>
+        <v>197.045</v>
       </c>
       <c r="F66">
-        <v>391.232</v>
+        <v>397.345</v>
       </c>
       <c r="G66">
         <v>0.823</v>
@@ -6705,37 +6705,37 @@
         <v>46.775</v>
       </c>
       <c r="M66">
-        <v>57.4328576</v>
+        <v>58.330246</v>
       </c>
       <c r="N66">
-        <v>-10.6578576</v>
+        <v>-11.555246</v>
       </c>
       <c r="O66">
-        <v>-2.984200128</v>
+        <v>-3.235468880000001</v>
       </c>
       <c r="P66">
-        <v>-7.673657471999999</v>
+        <v>-8.319777120000003</v>
       </c>
       <c r="Q66">
-        <v>15.426342528</v>
+        <v>14.78022288</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1039531501067751</v>
+        <v>0.1056146686812544</v>
       </c>
       <c r="T66">
-        <v>1.343028870826214</v>
+        <v>1.381401124278391</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2280401941901634</v>
+        <v>0.2245318835103147</v>
       </c>
       <c r="W66">
-        <v>0.113323699492884</v>
+        <v>0.1138387195006858</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8144292649648692</v>
+        <v>0.8018995839654096</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1109603017138848</v>
+        <v>0.1485723828559809</v>
       </c>
       <c r="C67">
-        <v>-185.8297195667062</v>
+        <v>-265.7484691238518</v>
       </c>
       <c r="D67">
-        <v>210.6922804332937</v>
+        <v>136.8865308761481</v>
       </c>
       <c r="E67">
-        <v>197.045</v>
+        <v>203.158</v>
       </c>
       <c r="F67">
-        <v>397.345</v>
+        <v>403.458</v>
       </c>
       <c r="G67">
         <v>0.823</v>
@@ -6787,45 +6787,45 @@
         <v>46.775</v>
       </c>
       <c r="M67">
-        <v>58.330246</v>
+        <v>81.0143664</v>
       </c>
       <c r="N67">
-        <v>-11.555246</v>
+        <v>-34.2393664</v>
       </c>
       <c r="O67">
-        <v>-3.235468880000001</v>
+        <v>-9.587022592000002</v>
       </c>
       <c r="P67">
-        <v>-8.319777120000003</v>
+        <v>-24.652343808</v>
       </c>
       <c r="Q67">
-        <v>14.78022288</v>
+        <v>-1.552343807999996</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1056146686812544</v>
+        <v>0.1102035740603975</v>
       </c>
       <c r="T67">
-        <v>1.381401124278391</v>
+        <v>1.487380463288627</v>
       </c>
       <c r="U67">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.2245318835103147</v>
+        <v>0.16166268505187</v>
       </c>
       <c r="W67">
-        <v>0.1138387195006858</v>
+        <v>0.1683381328415845</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8018995839654096</v>
+        <v>0.5773667323281071</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1485723828559809</v>
+        <v>0.150122382855981</v>
       </c>
       <c r="C68">
-        <v>-265.7484691238518</v>
+        <v>-273.8094378644267</v>
       </c>
       <c r="D68">
-        <v>136.8865308761481</v>
+        <v>134.9385621355732</v>
       </c>
       <c r="E68">
-        <v>203.158</v>
+        <v>209.271</v>
       </c>
       <c r="F68">
-        <v>403.458</v>
+        <v>409.571</v>
       </c>
       <c r="G68">
         <v>0.823</v>
@@ -6869,37 +6869,37 @@
         <v>46.775</v>
       </c>
       <c r="M68">
-        <v>81.0143664</v>
+        <v>82.24185679999999</v>
       </c>
       <c r="N68">
-        <v>-34.2393664</v>
+        <v>-35.4668568</v>
       </c>
       <c r="O68">
-        <v>-9.587022592000002</v>
+        <v>-9.930719904</v>
       </c>
       <c r="P68">
-        <v>-24.652343808</v>
+        <v>-25.536136896</v>
       </c>
       <c r="Q68">
-        <v>-1.552343807999996</v>
+        <v>-2.436136895999994</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1102035740603975</v>
+        <v>0.1121551975167732</v>
       </c>
       <c r="T68">
-        <v>1.487380463288627</v>
+        <v>1.532452598539797</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.16166268505187</v>
+        <v>0.1592498091555735</v>
       </c>
       <c r="W68">
-        <v>0.1683381328415845</v>
+        <v>0.1688226383215609</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5773667323281071</v>
+        <v>0.5687493184127623</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.150122382855981</v>
+        <v>0.1516723828559809</v>
       </c>
       <c r="C69">
-        <v>-273.8094378644267</v>
+        <v>-281.8157432147818</v>
       </c>
       <c r="D69">
-        <v>134.9385621355732</v>
+        <v>133.0452567852182</v>
       </c>
       <c r="E69">
-        <v>209.271</v>
+        <v>215.384</v>
       </c>
       <c r="F69">
-        <v>409.571</v>
+        <v>415.684</v>
       </c>
       <c r="G69">
         <v>0.823</v>
@@ -6951,37 +6951,37 @@
         <v>46.775</v>
       </c>
       <c r="M69">
-        <v>82.24185679999999</v>
+        <v>83.4693472</v>
       </c>
       <c r="N69">
-        <v>-35.4668568</v>
+        <v>-36.6943472</v>
       </c>
       <c r="O69">
-        <v>-9.930719904</v>
+        <v>-10.274417216</v>
       </c>
       <c r="P69">
-        <v>-25.536136896</v>
+        <v>-26.419929984</v>
       </c>
       <c r="Q69">
-        <v>-2.436136895999994</v>
+        <v>-3.319929983999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1121551975167732</v>
+        <v>0.1142287974391724</v>
       </c>
       <c r="T69">
-        <v>1.532452598539797</v>
+        <v>1.580341742244166</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1592498091555735</v>
+        <v>0.1569079001974032</v>
       </c>
       <c r="W69">
-        <v>0.1688226383215609</v>
+        <v>0.1692928936403614</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5687493184127623</v>
+        <v>0.5603853578478687</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1516723828559809</v>
+        <v>0.1532223828559809</v>
       </c>
       <c r="C70">
-        <v>-281.8157432147818</v>
+        <v>-289.7696542623251</v>
       </c>
       <c r="D70">
-        <v>133.0452567852182</v>
+        <v>131.2043457376749</v>
       </c>
       <c r="E70">
-        <v>215.384</v>
+        <v>221.497</v>
       </c>
       <c r="F70">
-        <v>415.684</v>
+        <v>421.797</v>
       </c>
       <c r="G70">
         <v>0.823</v>
@@ -7033,37 +7033,37 @@
         <v>46.775</v>
       </c>
       <c r="M70">
-        <v>83.4693472</v>
+        <v>84.69683760000001</v>
       </c>
       <c r="N70">
-        <v>-36.6943472</v>
+        <v>-37.92183760000001</v>
       </c>
       <c r="O70">
-        <v>-10.274417216</v>
+        <v>-10.618114528</v>
       </c>
       <c r="P70">
-        <v>-26.419929984</v>
+        <v>-27.30372307200001</v>
       </c>
       <c r="Q70">
-        <v>-3.319929983999998</v>
+        <v>-4.203723072000006</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1142287974391724</v>
+        <v>0.1164361780017263</v>
       </c>
       <c r="T70">
-        <v>1.580341742244166</v>
+        <v>1.63132050812301</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1569079001974032</v>
+        <v>0.1546338726583104</v>
       </c>
       <c r="W70">
-        <v>0.1692928936403614</v>
+        <v>0.1697495183702113</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5603853578478687</v>
+        <v>0.5522638309225372</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1532223828559809</v>
+        <v>0.1547723828559809</v>
       </c>
       <c r="C71">
-        <v>-289.7696542623251</v>
+        <v>-297.673316221479</v>
       </c>
       <c r="D71">
-        <v>131.2043457376749</v>
+        <v>129.4136837785211</v>
       </c>
       <c r="E71">
-        <v>221.497</v>
+        <v>227.61</v>
       </c>
       <c r="F71">
-        <v>421.797</v>
+        <v>427.91</v>
       </c>
       <c r="G71">
         <v>0.823</v>
@@ -7115,37 +7115,37 @@
         <v>46.775</v>
       </c>
       <c r="M71">
-        <v>84.69683760000001</v>
+        <v>85.924328</v>
       </c>
       <c r="N71">
-        <v>-37.92183760000001</v>
+        <v>-39.149328</v>
       </c>
       <c r="O71">
-        <v>-10.618114528</v>
+        <v>-10.96181184</v>
       </c>
       <c r="P71">
-        <v>-27.30372307200001</v>
+        <v>-28.18751616</v>
       </c>
       <c r="Q71">
-        <v>-4.203723072000006</v>
+        <v>-5.08751616</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1164361780017263</v>
+        <v>0.1187907172684505</v>
       </c>
       <c r="T71">
-        <v>1.63132050812301</v>
+        <v>1.685697858393777</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1546338726583104</v>
+        <v>0.1524248173346203</v>
       </c>
       <c r="W71">
-        <v>0.1697495183702113</v>
+        <v>0.1701930966792082</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5522638309225372</v>
+        <v>0.5443743476236439</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1547723828559809</v>
+        <v>0.1563223828559809</v>
       </c>
       <c r="C72">
-        <v>-297.673316221479</v>
+        <v>-305.5287587728899</v>
       </c>
       <c r="D72">
-        <v>129.4136837785211</v>
+        <v>127.6712412271102</v>
       </c>
       <c r="E72">
-        <v>227.61</v>
+        <v>233.723</v>
       </c>
       <c r="F72">
-        <v>427.91</v>
+        <v>434.023</v>
       </c>
       <c r="G72">
         <v>0.823</v>
@@ -7197,37 +7197,37 @@
         <v>46.775</v>
       </c>
       <c r="M72">
-        <v>85.924328</v>
+        <v>87.15181840000001</v>
       </c>
       <c r="N72">
-        <v>-39.149328</v>
+        <v>-40.37681840000001</v>
       </c>
       <c r="O72">
-        <v>-10.96181184</v>
+        <v>-11.305509152</v>
       </c>
       <c r="P72">
-        <v>-28.18751616</v>
+        <v>-29.07130924800001</v>
       </c>
       <c r="Q72">
-        <v>-5.08751616</v>
+        <v>-5.971309248000004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1187907172684505</v>
+        <v>0.1213076385535695</v>
       </c>
       <c r="T72">
-        <v>1.685697858393777</v>
+        <v>1.743825370752183</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1524248173346203</v>
+        <v>0.1502779889214566</v>
       </c>
       <c r="W72">
-        <v>0.1701930966792082</v>
+        <v>0.1706241798245715</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5443743476236439</v>
+        <v>0.5367071032909165</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1563223828559809</v>
+        <v>0.1578723828559809</v>
       </c>
       <c r="C73">
-        <v>-305.5287587728898</v>
+        <v>-313.3379037379061</v>
       </c>
       <c r="D73">
-        <v>127.6712412271102</v>
+        <v>125.9750962620939</v>
       </c>
       <c r="E73">
-        <v>233.723</v>
+        <v>239.836</v>
       </c>
       <c r="F73">
-        <v>434.023</v>
+        <v>440.136</v>
       </c>
       <c r="G73">
         <v>0.823</v>
@@ -7279,37 +7279,37 @@
         <v>46.775</v>
       </c>
       <c r="M73">
-        <v>87.1518184</v>
+        <v>88.37930879999999</v>
       </c>
       <c r="N73">
-        <v>-40.3768184</v>
+        <v>-41.60430879999999</v>
       </c>
       <c r="O73">
-        <v>-11.305509152</v>
+        <v>-11.649206464</v>
       </c>
       <c r="P73">
-        <v>-29.071309248</v>
+        <v>-29.95510233599999</v>
       </c>
       <c r="Q73">
-        <v>-5.971309247999997</v>
+        <v>-6.855102335999991</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1213076385535695</v>
+        <v>0.1240043399304827</v>
       </c>
       <c r="T73">
-        <v>1.743825370752183</v>
+        <v>1.806104848279046</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1502779889214566</v>
+        <v>0.1481907946308809</v>
       </c>
       <c r="W73">
-        <v>0.1706241798245715</v>
+        <v>0.1710432884381191</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5367071032909165</v>
+        <v>0.5292528379674316</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1578723828559809</v>
+        <v>0.1594223828559809</v>
       </c>
       <c r="C74">
-        <v>-313.3379037379061</v>
+        <v>-321.102572149333</v>
       </c>
       <c r="D74">
-        <v>125.9750962620939</v>
+        <v>124.323427850667</v>
       </c>
       <c r="E74">
-        <v>239.836</v>
+        <v>245.949</v>
       </c>
       <c r="F74">
-        <v>440.136</v>
+        <v>446.249</v>
       </c>
       <c r="G74">
         <v>0.823</v>
@@ -7361,37 +7361,37 @@
         <v>46.775</v>
       </c>
       <c r="M74">
-        <v>88.37930879999999</v>
+        <v>89.6067992</v>
       </c>
       <c r="N74">
-        <v>-41.60430879999999</v>
+        <v>-42.8317992</v>
       </c>
       <c r="O74">
-        <v>-11.649206464</v>
+        <v>-11.992903776</v>
       </c>
       <c r="P74">
-        <v>-29.95510233599999</v>
+        <v>-30.838895424</v>
       </c>
       <c r="Q74">
-        <v>-6.855102335999991</v>
+        <v>-7.738895423999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1240043399304827</v>
+        <v>0.126900796964945</v>
       </c>
       <c r="T74">
-        <v>1.806104848279046</v>
+        <v>1.872997620437529</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1481907946308809</v>
+        <v>0.1461607837455263</v>
       </c>
       <c r="W74">
-        <v>0.1710432884381191</v>
+        <v>0.1714509146238983</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5292528379674316</v>
+        <v>0.5220027990911653</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1594223828559809</v>
+        <v>0.1609723828559809</v>
       </c>
       <c r="C75">
-        <v>-321.102572149333</v>
+        <v>-328.824490773154</v>
       </c>
       <c r="D75">
-        <v>124.323427850667</v>
+        <v>122.714509226846</v>
       </c>
       <c r="E75">
-        <v>245.949</v>
+        <v>252.062</v>
       </c>
       <c r="F75">
-        <v>446.249</v>
+        <v>452.362</v>
       </c>
       <c r="G75">
         <v>0.823</v>
@@ -7443,37 +7443,37 @@
         <v>46.775</v>
       </c>
       <c r="M75">
-        <v>89.6067992</v>
+        <v>90.83428959999999</v>
       </c>
       <c r="N75">
-        <v>-42.8317992</v>
+        <v>-44.05928959999999</v>
       </c>
       <c r="O75">
-        <v>-11.992903776</v>
+        <v>-12.336601088</v>
       </c>
       <c r="P75">
-        <v>-30.838895424</v>
+        <v>-31.72268851199999</v>
       </c>
       <c r="Q75">
-        <v>-7.738895423999999</v>
+        <v>-8.622688511999993</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.126900796964945</v>
+        <v>0.1300200583866737</v>
       </c>
       <c r="T75">
-        <v>1.872997620437529</v>
+        <v>1.945035990454357</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1461607837455263</v>
+        <v>0.1441856380192354</v>
       </c>
       <c r="W75">
-        <v>0.1714509146238983</v>
+        <v>0.1718475238857375</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5220027990911653</v>
+        <v>0.5149487072115551</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1609723828559809</v>
+        <v>0.1625223828559809</v>
       </c>
       <c r="C76">
-        <v>-328.824490773154</v>
+        <v>-336.5052981303219</v>
       </c>
       <c r="D76">
-        <v>122.714509226846</v>
+        <v>121.146701869678</v>
       </c>
       <c r="E76">
-        <v>252.062</v>
+        <v>258.175</v>
       </c>
       <c r="F76">
-        <v>452.362</v>
+        <v>458.475</v>
       </c>
       <c r="G76">
         <v>0.823</v>
@@ -7525,37 +7525,37 @@
         <v>46.775</v>
       </c>
       <c r="M76">
-        <v>90.83428959999999</v>
+        <v>92.06178</v>
       </c>
       <c r="N76">
-        <v>-44.05928959999999</v>
+        <v>-45.28678</v>
       </c>
       <c r="O76">
-        <v>-12.336601088</v>
+        <v>-12.6802984</v>
       </c>
       <c r="P76">
-        <v>-31.72268851199999</v>
+        <v>-32.6064816</v>
       </c>
       <c r="Q76">
-        <v>-8.622688511999993</v>
+        <v>-9.506481599999994</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1300200583866737</v>
+        <v>0.1333888607221406</v>
       </c>
       <c r="T76">
-        <v>1.945035990454357</v>
+        <v>2.022837430072532</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1441856380192354</v>
+        <v>0.1422631628456456</v>
       </c>
       <c r="W76">
-        <v>0.1718475238857375</v>
+        <v>0.1722335569005944</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5149487072115551</v>
+        <v>0.5080827244487343</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1625223828559809</v>
+        <v>0.1640723828559809</v>
       </c>
       <c r="C77">
-        <v>-336.5052981303219</v>
+        <v>-344.1465500627642</v>
       </c>
       <c r="D77">
-        <v>121.146701869678</v>
+        <v>119.6184499372358</v>
       </c>
       <c r="E77">
-        <v>258.175</v>
+        <v>264.288</v>
       </c>
       <c r="F77">
-        <v>458.475</v>
+        <v>464.588</v>
       </c>
       <c r="G77">
         <v>0.823</v>
@@ -7607,37 +7607,37 @@
         <v>46.775</v>
       </c>
       <c r="M77">
-        <v>92.06178</v>
+        <v>93.28927039999999</v>
       </c>
       <c r="N77">
-        <v>-45.28678</v>
+        <v>-46.51427039999999</v>
       </c>
       <c r="O77">
-        <v>-12.6802984</v>
+        <v>-13.023995712</v>
       </c>
       <c r="P77">
-        <v>-32.6064816</v>
+        <v>-33.49027468799999</v>
       </c>
       <c r="Q77">
-        <v>-9.506481599999994</v>
+        <v>-10.39027468799999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1333888607221406</v>
+        <v>0.1370383965855632</v>
       </c>
       <c r="T77">
-        <v>2.022837430072532</v>
+        <v>2.107122322992221</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1422631628456456</v>
+        <v>0.1403912791239924</v>
       </c>
       <c r="W77">
-        <v>0.1722335569005944</v>
+        <v>0.1726094311519023</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5080827244487343</v>
+        <v>0.5013974254428299</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1640723828559809</v>
+        <v>0.1929605942174682</v>
       </c>
       <c r="C78">
-        <v>-344.1465500627642</v>
+        <v>-373.0296331247881</v>
       </c>
       <c r="D78">
-        <v>119.6184499372358</v>
+        <v>96.84836687521188</v>
       </c>
       <c r="E78">
-        <v>264.288</v>
+        <v>270.401</v>
       </c>
       <c r="F78">
-        <v>464.588</v>
+        <v>470.701</v>
       </c>
       <c r="G78">
         <v>0.823</v>
@@ -7689,45 +7689,45 @@
         <v>46.775</v>
       </c>
       <c r="M78">
-        <v>93.28927039999999</v>
+        <v>110.9912958</v>
       </c>
       <c r="N78">
-        <v>-46.51427039999999</v>
+        <v>-64.21629580000001</v>
       </c>
       <c r="O78">
-        <v>-13.023995712</v>
+        <v>-17.980562824</v>
       </c>
       <c r="P78">
-        <v>-33.49027468799999</v>
+        <v>-46.23573297600001</v>
       </c>
       <c r="Q78">
-        <v>-10.39027468799999</v>
+        <v>-23.13573297600001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1370383965855632</v>
+        <v>0.1426931588783585</v>
       </c>
       <c r="T78">
-        <v>2.107122322992221</v>
+        <v>2.237717295112205</v>
       </c>
       <c r="U78">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1403912791239924</v>
+        <v>0.1180002441236478</v>
       </c>
       <c r="W78">
-        <v>0.1726094311519023</v>
+        <v>0.2079755424356439</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.5013974254428299</v>
+        <v>0.4214294432987419</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1929605942174682</v>
+        <v>0.1948605942174682</v>
       </c>
       <c r="C79">
-        <v>-373.0296331247881</v>
+        <v>-380.3401679305385</v>
       </c>
       <c r="D79">
-        <v>96.84836687521188</v>
+        <v>95.65083206946146</v>
       </c>
       <c r="E79">
-        <v>270.401</v>
+        <v>276.514</v>
       </c>
       <c r="F79">
-        <v>470.701</v>
+        <v>476.814</v>
       </c>
       <c r="G79">
         <v>0.823</v>
@@ -7771,37 +7771,37 @@
         <v>46.775</v>
       </c>
       <c r="M79">
-        <v>110.9912958</v>
+        <v>112.4327412</v>
       </c>
       <c r="N79">
-        <v>-64.21629580000001</v>
+        <v>-65.6577412</v>
       </c>
       <c r="O79">
-        <v>-17.980562824</v>
+        <v>-18.384167536</v>
       </c>
       <c r="P79">
-        <v>-46.23573297600001</v>
+        <v>-47.273573664</v>
       </c>
       <c r="Q79">
-        <v>-23.13573297600001</v>
+        <v>-24.173573664</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1426931588783585</v>
+        <v>0.1470973933728293</v>
       </c>
       <c r="T79">
-        <v>2.237717295112205</v>
+        <v>2.339431717617305</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1180002441236478</v>
+        <v>0.1164874204810369</v>
       </c>
       <c r="W79">
-        <v>0.2079755424356439</v>
+        <v>0.2083322662505715</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4214294432987419</v>
+        <v>0.4160265017179888</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1948605942174682</v>
+        <v>0.1967605942174682</v>
       </c>
       <c r="C80">
-        <v>-380.3401679305385</v>
+        <v>-387.6214493032257</v>
       </c>
       <c r="D80">
-        <v>95.65083206946146</v>
+        <v>94.48255069677428</v>
       </c>
       <c r="E80">
-        <v>276.514</v>
+        <v>282.627</v>
       </c>
       <c r="F80">
-        <v>476.814</v>
+        <v>482.927</v>
       </c>
       <c r="G80">
         <v>0.823</v>
@@ -7853,37 +7853,37 @@
         <v>46.775</v>
       </c>
       <c r="M80">
-        <v>112.4327412</v>
+        <v>113.8741866</v>
       </c>
       <c r="N80">
-        <v>-65.6577412</v>
+        <v>-67.0991866</v>
       </c>
       <c r="O80">
-        <v>-18.384167536</v>
+        <v>-18.787772248</v>
       </c>
       <c r="P80">
-        <v>-47.273573664</v>
+        <v>-48.311414352</v>
       </c>
       <c r="Q80">
-        <v>-24.173573664</v>
+        <v>-25.211414352</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1470973933728293</v>
+        <v>0.1519210787715355</v>
       </c>
       <c r="T80">
-        <v>2.339431717617305</v>
+        <v>2.450833227980035</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1164874204810369</v>
+        <v>0.1150128961711503</v>
       </c>
       <c r="W80">
-        <v>0.2083322662505715</v>
+        <v>0.2086799590828428</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4160265017179888</v>
+        <v>0.4107603434683942</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1967605942174682</v>
+        <v>0.1986605942174682</v>
       </c>
       <c r="C81">
-        <v>-387.6214493032257</v>
+        <v>-394.874536214773</v>
       </c>
       <c r="D81">
-        <v>94.48255069677428</v>
+        <v>93.34246378522697</v>
       </c>
       <c r="E81">
-        <v>282.627</v>
+        <v>288.74</v>
       </c>
       <c r="F81">
-        <v>482.927</v>
+        <v>489.04</v>
       </c>
       <c r="G81">
         <v>0.823</v>
@@ -7935,37 +7935,37 @@
         <v>46.775</v>
       </c>
       <c r="M81">
-        <v>113.8741866</v>
+        <v>115.315632</v>
       </c>
       <c r="N81">
-        <v>-67.0991866</v>
+        <v>-68.54063199999999</v>
       </c>
       <c r="O81">
-        <v>-18.787772248</v>
+        <v>-19.19137696</v>
       </c>
       <c r="P81">
-        <v>-48.311414352</v>
+        <v>-49.34925503999999</v>
       </c>
       <c r="Q81">
-        <v>-25.211414352</v>
+        <v>-26.24925503999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1519210787715355</v>
+        <v>0.1572271327101122</v>
       </c>
       <c r="T81">
-        <v>2.450833227980035</v>
+        <v>2.573374889379036</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1150128961711503</v>
+        <v>0.113575234969011</v>
       </c>
       <c r="W81">
-        <v>0.2086799590828428</v>
+        <v>0.2090189595943072</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4107603434683942</v>
+        <v>0.4056258391750392</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1986605942174682</v>
+        <v>0.2005605942174682</v>
       </c>
       <c r="C82">
-        <v>-394.874536214773</v>
+        <v>-402.1004371335811</v>
       </c>
       <c r="D82">
-        <v>93.34246378522697</v>
+        <v>92.22956286641899</v>
       </c>
       <c r="E82">
-        <v>288.74</v>
+        <v>294.853</v>
       </c>
       <c r="F82">
-        <v>489.04</v>
+        <v>495.153</v>
       </c>
       <c r="G82">
         <v>0.823</v>
@@ -8017,37 +8017,37 @@
         <v>46.775</v>
       </c>
       <c r="M82">
-        <v>115.315632</v>
+        <v>116.7570774</v>
       </c>
       <c r="N82">
-        <v>-68.54063199999999</v>
+        <v>-69.98207740000001</v>
       </c>
       <c r="O82">
-        <v>-19.19137696</v>
+        <v>-19.594981672</v>
       </c>
       <c r="P82">
-        <v>-49.34925503999999</v>
+        <v>-50.38709572800001</v>
       </c>
       <c r="Q82">
-        <v>-26.24925503999999</v>
+        <v>-27.287095728</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1572271327101122</v>
+        <v>0.1630917186422234</v>
       </c>
       <c r="T82">
-        <v>2.573374889379036</v>
+        <v>2.708815673030565</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.113575234969011</v>
+        <v>0.1121730715743318</v>
       </c>
       <c r="W82">
-        <v>0.2090189595943072</v>
+        <v>0.2093495897227726</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4056258391750392</v>
+        <v>0.4006181127654708</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2005605942174682</v>
+        <v>0.2024605942174683</v>
       </c>
       <c r="C83">
-        <v>-402.1004371335811</v>
+        <v>-409.3001129997626</v>
       </c>
       <c r="D83">
-        <v>92.22956286641899</v>
+        <v>91.14288700023744</v>
       </c>
       <c r="E83">
-        <v>294.853</v>
+        <v>300.966</v>
       </c>
       <c r="F83">
-        <v>495.153</v>
+        <v>501.266</v>
       </c>
       <c r="G83">
         <v>0.823</v>
@@ -8099,37 +8099,37 @@
         <v>46.775</v>
       </c>
       <c r="M83">
-        <v>116.7570774</v>
+        <v>118.1985228</v>
       </c>
       <c r="N83">
-        <v>-69.98207740000001</v>
+        <v>-71.4235228</v>
       </c>
       <c r="O83">
-        <v>-19.594981672</v>
+        <v>-19.998586384</v>
       </c>
       <c r="P83">
-        <v>-50.38709572800001</v>
+        <v>-51.42493641599999</v>
       </c>
       <c r="Q83">
-        <v>-27.287095728</v>
+        <v>-28.32493641599999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1630917186422234</v>
+        <v>0.1696079252334581</v>
       </c>
       <c r="T83">
-        <v>2.708815673030565</v>
+        <v>2.859305432643374</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1121730715743318</v>
+        <v>0.11080510728684</v>
       </c>
       <c r="W83">
-        <v>0.2093495897227726</v>
+        <v>0.2096721557017631</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4006181127654708</v>
+        <v>0.3957325260244284</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2024605942174683</v>
+        <v>0.2043605942174682</v>
       </c>
       <c r="C84">
-        <v>-409.3001129997626</v>
+        <v>-416.4744799925011</v>
       </c>
       <c r="D84">
-        <v>91.14288700023744</v>
+        <v>90.08152000749892</v>
       </c>
       <c r="E84">
-        <v>300.966</v>
+        <v>307.079</v>
       </c>
       <c r="F84">
-        <v>501.266</v>
+        <v>507.379</v>
       </c>
       <c r="G84">
         <v>0.823</v>
@@ -8181,37 +8181,37 @@
         <v>46.775</v>
       </c>
       <c r="M84">
-        <v>118.1985228</v>
+        <v>119.6399682</v>
       </c>
       <c r="N84">
-        <v>-71.4235228</v>
+        <v>-72.86496820000002</v>
       </c>
       <c r="O84">
-        <v>-19.998586384</v>
+        <v>-20.40219109600001</v>
       </c>
       <c r="P84">
-        <v>-51.42493641599999</v>
+        <v>-52.46277710400001</v>
       </c>
       <c r="Q84">
-        <v>-28.32493641599999</v>
+        <v>-29.36277710400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1696079252334581</v>
+        <v>0.176890744364838</v>
       </c>
       <c r="T84">
-        <v>2.859305432643374</v>
+        <v>3.02749986985769</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.11080510728684</v>
+        <v>0.1094701059942274</v>
       </c>
       <c r="W84">
-        <v>0.2096721557017631</v>
+        <v>0.2099869490065612</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3957325260244284</v>
+        <v>0.3909646642650979</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2043605942174682</v>
+        <v>0.2062605942174682</v>
       </c>
       <c r="C85">
-        <v>-416.4744799925011</v>
+        <v>-423.6244121062728</v>
       </c>
       <c r="D85">
-        <v>90.08152000749892</v>
+        <v>89.04458789372724</v>
       </c>
       <c r="E85">
-        <v>307.079</v>
+        <v>313.192</v>
       </c>
       <c r="F85">
-        <v>507.379</v>
+        <v>513.492</v>
       </c>
       <c r="G85">
         <v>0.823</v>
@@ -8263,37 +8263,37 @@
         <v>46.775</v>
       </c>
       <c r="M85">
-        <v>119.6399682</v>
+        <v>121.0814136</v>
       </c>
       <c r="N85">
-        <v>-72.86496820000002</v>
+        <v>-74.30641359999998</v>
       </c>
       <c r="O85">
-        <v>-20.40219109600001</v>
+        <v>-20.805795808</v>
       </c>
       <c r="P85">
-        <v>-52.46277710400001</v>
+        <v>-53.50061779199999</v>
       </c>
       <c r="Q85">
-        <v>-29.36277710400001</v>
+        <v>-30.40061779199998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.176890744364838</v>
+        <v>0.1850839158876404</v>
       </c>
       <c r="T85">
-        <v>3.02749986985769</v>
+        <v>3.216718611723796</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1094701059942274</v>
+        <v>0.1081668904466771</v>
       </c>
       <c r="W85">
-        <v>0.2099869490065612</v>
+        <v>0.2102942472326735</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3909646642650979</v>
+        <v>0.3863103230238469</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2062605942174682</v>
+        <v>0.2081605942174682</v>
       </c>
       <c r="C86">
-        <v>-423.6244121062728</v>
+        <v>-430.7507435511668</v>
       </c>
       <c r="D86">
-        <v>89.04458789372724</v>
+        <v>88.03125644883308</v>
       </c>
       <c r="E86">
-        <v>313.192</v>
+        <v>319.3049999999999</v>
       </c>
       <c r="F86">
-        <v>513.492</v>
+        <v>519.6049999999999</v>
       </c>
       <c r="G86">
         <v>0.823</v>
@@ -8345,37 +8345,37 @@
         <v>46.775</v>
       </c>
       <c r="M86">
-        <v>121.0814136</v>
+        <v>122.522859</v>
       </c>
       <c r="N86">
-        <v>-74.30641359999998</v>
+        <v>-75.74785899999998</v>
       </c>
       <c r="O86">
-        <v>-20.805795808</v>
+        <v>-21.20940052</v>
       </c>
       <c r="P86">
-        <v>-53.50061779199999</v>
+        <v>-54.53845847999998</v>
       </c>
       <c r="Q86">
-        <v>-30.40061779199998</v>
+        <v>-31.43845847999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1850839158876403</v>
+        <v>0.1943695102801496</v>
       </c>
       <c r="T86">
-        <v>3.216718611723794</v>
+        <v>3.431166519172047</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1081668904466771</v>
+        <v>0.1068943387943633</v>
       </c>
       <c r="W86">
-        <v>0.2102942472326735</v>
+        <v>0.2105943149122891</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3863103230238469</v>
+        <v>0.3817654956941546</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2081605942174682</v>
+        <v>0.2100605942174682</v>
       </c>
       <c r="C87">
-        <v>-430.7507435511668</v>
+        <v>-437.8542709911551</v>
       </c>
       <c r="D87">
-        <v>88.03125644883308</v>
+        <v>87.04072900884488</v>
       </c>
       <c r="E87">
-        <v>319.3049999999999</v>
+        <v>325.4179999999999</v>
       </c>
       <c r="F87">
-        <v>519.6049999999999</v>
+        <v>525.718</v>
       </c>
       <c r="G87">
         <v>0.823</v>
@@ -8427,37 +8427,37 @@
         <v>46.775</v>
       </c>
       <c r="M87">
-        <v>122.522859</v>
+        <v>123.9643044</v>
       </c>
       <c r="N87">
-        <v>-75.74785899999998</v>
+        <v>-77.1893044</v>
       </c>
       <c r="O87">
-        <v>-21.20940052</v>
+        <v>-21.613005232</v>
       </c>
       <c r="P87">
-        <v>-54.53845847999998</v>
+        <v>-55.57629916799999</v>
       </c>
       <c r="Q87">
-        <v>-31.43845847999998</v>
+        <v>-32.47629916799999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1943695102801496</v>
+        <v>0.2049816181573032</v>
       </c>
       <c r="T87">
-        <v>3.431166519172047</v>
+        <v>3.67624984197005</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1068943387943633</v>
+        <v>0.1056513813665218</v>
       </c>
       <c r="W87">
-        <v>0.2105943149122891</v>
+        <v>0.2108874042737741</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3817654956941546</v>
+        <v>0.3773263620232922</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2100605942174682</v>
+        <v>0.2119605942174682</v>
       </c>
       <c r="C88">
-        <v>-437.8542709911551</v>
+        <v>-444.9357556329311</v>
       </c>
       <c r="D88">
-        <v>87.04072900884488</v>
+        <v>86.07224436706881</v>
       </c>
       <c r="E88">
-        <v>325.4179999999999</v>
+        <v>331.5309999999999</v>
       </c>
       <c r="F88">
-        <v>525.718</v>
+        <v>531.8309999999999</v>
       </c>
       <c r="G88">
         <v>0.823</v>
@@ -8509,37 +8509,37 @@
         <v>46.775</v>
       </c>
       <c r="M88">
-        <v>123.9643044</v>
+        <v>125.4057498</v>
       </c>
       <c r="N88">
-        <v>-77.1893044</v>
+        <v>-78.63074979999999</v>
       </c>
       <c r="O88">
-        <v>-21.613005232</v>
+        <v>-22.016609944</v>
       </c>
       <c r="P88">
-        <v>-55.57629916799999</v>
+        <v>-56.61413985599999</v>
       </c>
       <c r="Q88">
-        <v>-32.47629916799999</v>
+        <v>-33.51413985599999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2049816181573032</v>
+        <v>0.2172263580155573</v>
       </c>
       <c r="T88">
-        <v>3.67624984197005</v>
+        <v>3.959038291352362</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1056513813665218</v>
+        <v>0.1044369976726538</v>
       </c>
       <c r="W88">
-        <v>0.2108874042737741</v>
+        <v>0.2111737559487882</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3773263620232922</v>
+        <v>0.3729892774023349</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2119605942174682</v>
+        <v>0.2138605942174683</v>
       </c>
       <c r="C89">
-        <v>-444.9357556329311</v>
+        <v>-451.9959251768342</v>
       </c>
       <c r="D89">
-        <v>86.07224436706881</v>
+        <v>85.12507482316575</v>
       </c>
       <c r="E89">
-        <v>331.5309999999999</v>
+        <v>337.6439999999999</v>
       </c>
       <c r="F89">
-        <v>531.8309999999999</v>
+        <v>537.944</v>
       </c>
       <c r="G89">
         <v>0.823</v>
@@ -8591,37 +8591,37 @@
         <v>46.775</v>
       </c>
       <c r="M89">
-        <v>125.4057498</v>
+        <v>126.8471952</v>
       </c>
       <c r="N89">
-        <v>-78.63074979999999</v>
+        <v>-80.07219520000001</v>
       </c>
       <c r="O89">
-        <v>-22.016609944</v>
+        <v>-22.42021465600001</v>
       </c>
       <c r="P89">
-        <v>-56.61413985599999</v>
+        <v>-57.651980544</v>
       </c>
       <c r="Q89">
-        <v>-33.51413985599999</v>
+        <v>-34.551980544</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2172263580155573</v>
+        <v>0.2315118878501871</v>
       </c>
       <c r="T89">
-        <v>3.959038291352362</v>
+        <v>4.28895814896506</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1044369976726538</v>
+        <v>0.1032502136081918</v>
       </c>
       <c r="W89">
-        <v>0.2111737559487882</v>
+        <v>0.2114535996311884</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3729892774023349</v>
+        <v>0.3687507628863992</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2138605942174683</v>
+        <v>0.2157605942174682</v>
       </c>
       <c r="C90">
-        <v>-451.9959251768342</v>
+        <v>-459.0354756403599</v>
       </c>
       <c r="D90">
-        <v>85.12507482316575</v>
+        <v>84.19852435964016</v>
       </c>
       <c r="E90">
-        <v>337.6439999999999</v>
+        <v>343.757</v>
       </c>
       <c r="F90">
-        <v>537.944</v>
+        <v>544.057</v>
       </c>
       <c r="G90">
         <v>0.823</v>
@@ -8673,37 +8673,37 @@
         <v>46.775</v>
       </c>
       <c r="M90">
-        <v>126.8471952</v>
+        <v>128.2886406</v>
       </c>
       <c r="N90">
-        <v>-80.07219520000001</v>
+        <v>-81.5136406</v>
       </c>
       <c r="O90">
-        <v>-22.42021465600001</v>
+        <v>-22.823819368</v>
       </c>
       <c r="P90">
-        <v>-57.651980544</v>
+        <v>-58.689821232</v>
       </c>
       <c r="Q90">
-        <v>-34.551980544</v>
+        <v>-35.589821232</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2315118878501871</v>
+        <v>0.2483947867456586</v>
       </c>
       <c r="T90">
-        <v>4.28895814896506</v>
+        <v>4.67886343523461</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1032502136081918</v>
+        <v>0.1020900988485492</v>
       </c>
       <c r="W90">
-        <v>0.2114535996311884</v>
+        <v>0.2117271546915121</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3687507628863992</v>
+        <v>0.3646074958876757</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2157605942174682</v>
+        <v>0.2176605942174682</v>
       </c>
       <c r="C91">
-        <v>-459.0354756403599</v>
+        <v>-466.0550730638682</v>
       </c>
       <c r="D91">
-        <v>84.19852435964016</v>
+        <v>83.29192693613172</v>
       </c>
       <c r="E91">
-        <v>343.757</v>
+        <v>349.8699999999999</v>
       </c>
       <c r="F91">
-        <v>544.057</v>
+        <v>550.17</v>
       </c>
       <c r="G91">
         <v>0.823</v>
@@ -8755,37 +8755,37 @@
         <v>46.775</v>
       </c>
       <c r="M91">
-        <v>128.2886406</v>
+        <v>129.730086</v>
       </c>
       <c r="N91">
-        <v>-81.5136406</v>
+        <v>-82.95508599999999</v>
       </c>
       <c r="O91">
-        <v>-22.823819368</v>
+        <v>-23.22742408</v>
       </c>
       <c r="P91">
-        <v>-58.689821232</v>
+        <v>-59.72766191999999</v>
       </c>
       <c r="Q91">
-        <v>-35.589821232</v>
+        <v>-36.62766191999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2483947867456586</v>
+        <v>0.2686542654202245</v>
       </c>
       <c r="T91">
-        <v>4.67886343523461</v>
+        <v>5.146749778758071</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1020900988485492</v>
+        <v>0.1009557644168986</v>
       </c>
       <c r="W91">
-        <v>0.2117271546915121</v>
+        <v>0.2119946307504953</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3646074958876757</v>
+        <v>0.3605563014889237</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2176605942174682</v>
+        <v>0.2195605942174682</v>
       </c>
       <c r="C92">
-        <v>-466.0550730638682</v>
+        <v>-473.0553551072655</v>
       </c>
       <c r="D92">
-        <v>83.29192693613172</v>
+        <v>82.40464489273448</v>
       </c>
       <c r="E92">
-        <v>349.8699999999999</v>
+        <v>355.983</v>
       </c>
       <c r="F92">
-        <v>550.17</v>
+        <v>556.283</v>
       </c>
       <c r="G92">
         <v>0.823</v>
@@ -8837,37 +8837,37 @@
         <v>46.775</v>
       </c>
       <c r="M92">
-        <v>129.730086</v>
+        <v>131.1715314</v>
       </c>
       <c r="N92">
-        <v>-82.95508599999999</v>
+        <v>-84.39653140000001</v>
       </c>
       <c r="O92">
-        <v>-23.22742408</v>
+        <v>-23.63102879200001</v>
       </c>
       <c r="P92">
-        <v>-59.72766191999999</v>
+        <v>-60.76550260800001</v>
       </c>
       <c r="Q92">
-        <v>-36.62766191999999</v>
+        <v>-37.665502608</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2686542654202245</v>
+        <v>0.2934158504669162</v>
       </c>
       <c r="T92">
-        <v>5.146749778758071</v>
+        <v>5.718610865286748</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1009557644168986</v>
+        <v>0.09984636041231733</v>
       </c>
       <c r="W92">
-        <v>0.2119946307504953</v>
+        <v>0.2122562282147756</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3605563014889237</v>
+        <v>0.3565941443297047</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2195605942174682</v>
+        <v>0.2214605942174682</v>
       </c>
       <c r="C93">
-        <v>-473.0553551072655</v>
+        <v>-480.0369325457116</v>
       </c>
       <c r="D93">
-        <v>82.40464489273448</v>
+        <v>81.53606745428837</v>
       </c>
       <c r="E93">
-        <v>355.983</v>
+        <v>362.0959999999999</v>
       </c>
       <c r="F93">
-        <v>556.283</v>
+        <v>562.396</v>
       </c>
       <c r="G93">
         <v>0.823</v>
@@ -8919,37 +8919,37 @@
         <v>46.775</v>
       </c>
       <c r="M93">
-        <v>131.1715314</v>
+        <v>132.6129768</v>
       </c>
       <c r="N93">
-        <v>-84.39653140000001</v>
+        <v>-85.83797679999998</v>
       </c>
       <c r="O93">
-        <v>-23.63102879200001</v>
+        <v>-24.03463350399999</v>
       </c>
       <c r="P93">
-        <v>-60.76550260800001</v>
+        <v>-61.80334329599998</v>
       </c>
       <c r="Q93">
-        <v>-37.665502608</v>
+        <v>-38.70334329599998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2934158504669162</v>
+        <v>0.3243678317752807</v>
       </c>
       <c r="T93">
-        <v>5.718610865286748</v>
+        <v>6.433437223447592</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09984636041231733</v>
+        <v>0.09876107388609652</v>
       </c>
       <c r="W93">
-        <v>0.2122562282147756</v>
+        <v>0.2125121387776584</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3565941443297047</v>
+        <v>0.3527181210217732</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2214605942174682</v>
+        <v>0.2233605942174682</v>
       </c>
       <c r="C94">
-        <v>-480.0369325457116</v>
+        <v>-487.0003906717197</v>
       </c>
       <c r="D94">
-        <v>81.53606745428837</v>
+        <v>80.68560932828031</v>
       </c>
       <c r="E94">
-        <v>362.0959999999999</v>
+        <v>368.209</v>
       </c>
       <c r="F94">
-        <v>562.396</v>
+        <v>568.509</v>
       </c>
       <c r="G94">
         <v>0.823</v>
@@ -9001,37 +9001,37 @@
         <v>46.775</v>
       </c>
       <c r="M94">
-        <v>132.6129768</v>
+        <v>134.0544222</v>
       </c>
       <c r="N94">
-        <v>-85.83797679999998</v>
+        <v>-87.2794222</v>
       </c>
       <c r="O94">
-        <v>-24.03463350399999</v>
+        <v>-24.438238216</v>
       </c>
       <c r="P94">
-        <v>-61.80334329599998</v>
+        <v>-62.841183984</v>
       </c>
       <c r="Q94">
-        <v>-38.70334329599998</v>
+        <v>-39.741183984</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3243678317752807</v>
+        <v>0.3641632363146066</v>
       </c>
       <c r="T94">
-        <v>6.433437223447592</v>
+        <v>7.352499683940106</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09876107388609652</v>
+        <v>0.09769912685506321</v>
       </c>
       <c r="W94">
-        <v>0.2125121387776584</v>
+        <v>0.2127625458875761</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3527181210217732</v>
+        <v>0.3489254530537972</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2233605942174682</v>
+        <v>0.2252605942174682</v>
       </c>
       <c r="C95">
-        <v>-487.0003906717197</v>
+        <v>-493.9462906104147</v>
       </c>
       <c r="D95">
-        <v>80.68560932828031</v>
+        <v>79.85270938958526</v>
       </c>
       <c r="E95">
-        <v>368.209</v>
+        <v>374.3219999999999</v>
       </c>
       <c r="F95">
-        <v>568.509</v>
+        <v>574.622</v>
       </c>
       <c r="G95">
         <v>0.823</v>
@@ -9083,37 +9083,37 @@
         <v>46.775</v>
       </c>
       <c r="M95">
-        <v>134.0544222</v>
+        <v>135.4958676</v>
       </c>
       <c r="N95">
-        <v>-87.2794222</v>
+        <v>-88.72086759999999</v>
       </c>
       <c r="O95">
-        <v>-24.438238216</v>
+        <v>-24.841842928</v>
       </c>
       <c r="P95">
-        <v>-62.841183984</v>
+        <v>-63.87902467199999</v>
       </c>
       <c r="Q95">
-        <v>-39.741183984</v>
+        <v>-40.77902467199999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3641632363146066</v>
+        <v>0.4172237757003744</v>
       </c>
       <c r="T95">
-        <v>7.352499683940106</v>
+        <v>8.577916297930125</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09769912685506321</v>
+        <v>0.09665977444171148</v>
       </c>
       <c r="W95">
-        <v>0.2127625458875761</v>
+        <v>0.2130076251866445</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3489254530537972</v>
+        <v>0.3452134801489696</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2252605942174682</v>
+        <v>0.2271605942174682</v>
       </c>
       <c r="C96">
-        <v>-493.9462906104147</v>
+        <v>-500.8751705541637</v>
       </c>
       <c r="D96">
-        <v>79.85270938958526</v>
+        <v>79.0368294458363</v>
       </c>
       <c r="E96">
-        <v>374.3219999999999</v>
+        <v>380.435</v>
       </c>
       <c r="F96">
-        <v>574.622</v>
+        <v>580.735</v>
       </c>
       <c r="G96">
         <v>0.823</v>
@@ -9165,37 +9165,37 @@
         <v>46.775</v>
       </c>
       <c r="M96">
-        <v>135.4958676</v>
+        <v>136.937313</v>
       </c>
       <c r="N96">
-        <v>-88.72086759999999</v>
+        <v>-90.16231300000001</v>
       </c>
       <c r="O96">
-        <v>-24.841842928</v>
+        <v>-25.24544764000001</v>
       </c>
       <c r="P96">
-        <v>-63.87902467199999</v>
+        <v>-64.91686536</v>
       </c>
       <c r="Q96">
-        <v>-40.77902467199999</v>
+        <v>-41.81686536</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4172237757003744</v>
+        <v>0.4915085308404495</v>
       </c>
       <c r="T96">
-        <v>8.577916297930125</v>
+        <v>10.29349955751616</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09665977444171148</v>
+        <v>0.09564230313179871</v>
       </c>
       <c r="W96">
-        <v>0.2130076251866445</v>
+        <v>0.2132475449215219</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3452134801489696</v>
+        <v>0.3415796540421382</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2271605942174682</v>
+        <v>0.2290605942174682</v>
       </c>
       <c r="C97">
-        <v>-500.8751705541637</v>
+        <v>-507.7875469222801</v>
       </c>
       <c r="D97">
-        <v>79.0368294458363</v>
+        <v>78.23745307771986</v>
       </c>
       <c r="E97">
-        <v>380.435</v>
+        <v>386.5479999999999</v>
       </c>
       <c r="F97">
-        <v>580.735</v>
+        <v>586.848</v>
       </c>
       <c r="G97">
         <v>0.823</v>
@@ -9247,37 +9247,37 @@
         <v>46.775</v>
       </c>
       <c r="M97">
-        <v>136.937313</v>
+        <v>138.3787584</v>
       </c>
       <c r="N97">
-        <v>-90.16231300000001</v>
+        <v>-91.6037584</v>
       </c>
       <c r="O97">
-        <v>-25.24544764000001</v>
+        <v>-25.649052352</v>
       </c>
       <c r="P97">
-        <v>-64.91686536</v>
+        <v>-65.95470604800001</v>
       </c>
       <c r="Q97">
-        <v>-41.81686536</v>
+        <v>-42.854706048</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4915085308404495</v>
+        <v>0.6029356635505622</v>
       </c>
       <c r="T97">
-        <v>10.29349955751616</v>
+        <v>12.8668744468952</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09564230313179871</v>
+        <v>0.09464602914084247</v>
       </c>
       <c r="W97">
-        <v>0.2132475449215219</v>
+        <v>0.2134824663285894</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3415796540421382</v>
+        <v>0.338021532645866</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2290605942174682</v>
+        <v>0.2309605942174682</v>
       </c>
       <c r="C98">
-        <v>-507.7875469222799</v>
+        <v>-514.6839154510611</v>
       </c>
       <c r="D98">
-        <v>78.23745307772008</v>
+        <v>77.45408454893877</v>
       </c>
       <c r="E98">
-        <v>386.5479999999999</v>
+        <v>392.6609999999999</v>
       </c>
       <c r="F98">
-        <v>586.848</v>
+        <v>592.9609999999999</v>
       </c>
       <c r="G98">
         <v>0.823</v>
@@ -9329,37 +9329,37 @@
         <v>46.775</v>
       </c>
       <c r="M98">
-        <v>138.3787584</v>
+        <v>139.8202038</v>
       </c>
       <c r="N98">
-        <v>-91.6037584</v>
+        <v>-93.04520379999997</v>
       </c>
       <c r="O98">
-        <v>-25.649052352</v>
+        <v>-26.05265706399999</v>
       </c>
       <c r="P98">
-        <v>-65.95470604800001</v>
+        <v>-66.99254673599998</v>
       </c>
       <c r="Q98">
-        <v>-42.854706048</v>
+        <v>-43.89254673599998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6029356635505607</v>
+        <v>0.7886475514007475</v>
       </c>
       <c r="T98">
-        <v>12.86687444689517</v>
+        <v>17.15583259586022</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09464602914084247</v>
+        <v>0.09367029688165855</v>
       </c>
       <c r="W98">
-        <v>0.2134824663285894</v>
+        <v>0.2137125439953049</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.338021532645866</v>
+        <v>0.334536774577352</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2309605942174682</v>
+        <v>0.2328605942174682</v>
       </c>
       <c r="C99">
-        <v>-514.6839154510611</v>
+        <v>-521.5647522189871</v>
       </c>
       <c r="D99">
-        <v>77.45408454893877</v>
+        <v>76.68624778101288</v>
       </c>
       <c r="E99">
-        <v>392.6609999999999</v>
+        <v>398.7739999999999</v>
       </c>
       <c r="F99">
-        <v>592.9609999999999</v>
+        <v>599.074</v>
       </c>
       <c r="G99">
         <v>0.823</v>
@@ -9411,37 +9411,37 @@
         <v>46.775</v>
       </c>
       <c r="M99">
-        <v>139.8202038</v>
+        <v>141.2616492</v>
       </c>
       <c r="N99">
-        <v>-93.04520379999997</v>
+        <v>-94.48664919999999</v>
       </c>
       <c r="O99">
-        <v>-26.05265706399999</v>
+        <v>-26.456261776</v>
       </c>
       <c r="P99">
-        <v>-66.99254673599998</v>
+        <v>-68.030387424</v>
       </c>
       <c r="Q99">
-        <v>-43.89254673599998</v>
+        <v>-44.930387424</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7886475514007475</v>
+        <v>1.160071327101122</v>
       </c>
       <c r="T99">
-        <v>17.15583259586022</v>
+        <v>25.73374889379033</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09367029688165855</v>
+        <v>0.09271447752572325</v>
       </c>
       <c r="W99">
-        <v>0.2137125439953049</v>
+        <v>0.2139379261994345</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.334536774577352</v>
+        <v>0.3311231340204401</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2328605942174682</v>
+        <v>0.2347605942174682</v>
       </c>
       <c r="C100">
-        <v>-521.5647522189871</v>
+        <v>-528.4305146115398</v>
       </c>
       <c r="D100">
-        <v>76.68624778101288</v>
+        <v>75.93348538846011</v>
       </c>
       <c r="E100">
-        <v>398.7739999999999</v>
+        <v>404.8869999999999</v>
       </c>
       <c r="F100">
-        <v>599.074</v>
+        <v>605.1869999999999</v>
       </c>
       <c r="G100">
         <v>0.823</v>
@@ -9493,37 +9493,37 @@
         <v>46.775</v>
       </c>
       <c r="M100">
-        <v>141.2616492</v>
+        <v>142.7030946</v>
       </c>
       <c r="N100">
-        <v>-94.48664919999999</v>
+        <v>-95.92809459999998</v>
       </c>
       <c r="O100">
-        <v>-26.456261776</v>
+        <v>-26.859866488</v>
       </c>
       <c r="P100">
-        <v>-68.030387424</v>
+        <v>-69.06822811199999</v>
       </c>
       <c r="Q100">
-        <v>-44.930387424</v>
+        <v>-45.96822811199998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.160071327101122</v>
+        <v>2.274342654202242</v>
       </c>
       <c r="T100">
-        <v>25.73374889379033</v>
+        <v>51.46749778758066</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09271447752572325</v>
+        <v>0.09177796765172604</v>
       </c>
       <c r="W100">
-        <v>0.2139379261994345</v>
+        <v>0.214158755227723</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3311231340204401</v>
+        <v>0.3277784558990217</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2347605942174682</v>
-      </c>
-      <c r="C101">
-        <v>-528.4305146115398</v>
-      </c>
-      <c r="D101">
-        <v>75.93348538846011</v>
-      </c>
-      <c r="E101">
-        <v>404.8869999999999</v>
-      </c>
-      <c r="F101">
-        <v>605.1869999999999</v>
-      </c>
-      <c r="G101">
-        <v>0.823</v>
-      </c>
-      <c r="H101">
-        <v>411</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>69.875</v>
-      </c>
-      <c r="K101">
-        <v>23.1</v>
-      </c>
-      <c r="L101">
-        <v>46.775</v>
-      </c>
-      <c r="M101">
-        <v>142.7030946</v>
-      </c>
-      <c r="N101">
-        <v>-95.92809459999998</v>
-      </c>
-      <c r="O101">
-        <v>-26.859866488</v>
-      </c>
-      <c r="P101">
-        <v>-69.06822811199999</v>
-      </c>
-      <c r="Q101">
-        <v>-45.96822811199998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.274342654202242</v>
-      </c>
-      <c r="T101">
-        <v>51.46749778758066</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09177796765172604</v>
-      </c>
-      <c r="W101">
-        <v>0.214158755227723</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3277784558990217</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
